--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,12 +119,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,9 +131,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -681,11 +683,11 @@
       <c r="N6" s="6" t="n">
         <v>333678.88</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="6">
         <f>SUM(C6:N6)</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="6">
         <f>SUM(L6:N6)</f>
         <v/>
       </c>
@@ -737,11 +739,11 @@
       <c r="N7" s="6" t="n">
         <v>-7079.81</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="6">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="6">
         <f>SUM(L7:N7)</f>
         <v/>
       </c>
@@ -793,11 +795,11 @@
       <c r="N8" s="6" t="n">
         <v>-19247.76</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="6">
         <f>SUM(C8:N8)</f>
         <v/>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="6">
         <f>SUM(L8:N8)</f>
         <v/>
       </c>
@@ -849,11 +851,11 @@
       <c r="N9" s="6" t="n">
         <v>-3654.47</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="6">
         <f>SUM(C9:N9)</f>
         <v/>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="6">
         <f>SUM(L9:N9)</f>
         <v/>
       </c>
@@ -905,11 +907,11 @@
       <c r="N10" s="6" t="n">
         <v>-1344.54</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="6">
         <f>SUM(C10:N10)</f>
         <v/>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="6">
         <f>SUM(L10:N10)</f>
         <v/>
       </c>
@@ -961,11 +963,11 @@
       <c r="N11" s="6" t="n">
         <v>-2320.94</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <f>SUM(C11:N11)</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="6">
         <f>SUM(L11:N11)</f>
         <v/>
       </c>
@@ -1017,11 +1019,11 @@
       <c r="N12" s="6" t="n">
         <v>10254.61</v>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="6">
         <f>SUM(C12:N12)</f>
         <v/>
       </c>
-      <c r="P12" s="7">
+      <c r="P12" s="6">
         <f>SUM(L12:N12)</f>
         <v/>
       </c>
@@ -1073,11 +1075,11 @@
       <c r="N13" s="6" t="n">
         <v>4420.55</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="6">
         <f>SUM(C13:N13)</f>
         <v/>
       </c>
-      <c r="P13" s="7">
+      <c r="P13" s="6">
         <f>SUM(L13:N13)</f>
         <v/>
       </c>
@@ -1129,11 +1131,11 @@
       <c r="N14" s="6" t="n">
         <v>4033.37</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="6">
         <f>SUM(C14:N14)</f>
         <v/>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="6">
         <f>SUM(L14:N14)</f>
         <v/>
       </c>
@@ -1185,11 +1187,11 @@
       <c r="N15" s="6" t="n">
         <v>3226.21</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="6">
         <f>SUM(C15:N15)</f>
         <v/>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="6">
         <f>SUM(L15:N15)</f>
         <v/>
       </c>
@@ -1241,11 +1243,11 @@
       <c r="N16" s="6" t="n">
         <v>1524.71</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="6">
         <f>SUM(C16:N16)</f>
         <v/>
       </c>
-      <c r="P16" s="7">
+      <c r="P16" s="6">
         <f>SUM(L16:N16)</f>
         <v/>
       </c>
@@ -1297,11 +1299,11 @@
       <c r="N17" s="6" t="n">
         <v>1242.85</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O17" s="6">
         <f>SUM(C17:N17)</f>
         <v/>
       </c>
-      <c r="P17" s="7">
+      <c r="P17" s="6">
         <f>SUM(L17:N17)</f>
         <v/>
       </c>
@@ -1353,11 +1355,11 @@
       <c r="N18" s="6" t="n">
         <v>796.39</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O18" s="6">
         <f>SUM(C18:N18)</f>
         <v/>
       </c>
-      <c r="P18" s="7">
+      <c r="P18" s="6">
         <f>SUM(L18:N18)</f>
         <v/>
       </c>
@@ -1409,11 +1411,11 @@
       <c r="N19" s="6" t="n">
         <v>434.45</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <f>SUM(C19:N19)</f>
         <v/>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="6">
         <f>SUM(L19:N19)</f>
         <v/>
       </c>
@@ -1465,11 +1467,11 @@
       <c r="N20" s="6" t="n">
         <v>5383.49</v>
       </c>
-      <c r="O20" s="7">
+      <c r="O20" s="6">
         <f>SUM(C20:N20)</f>
         <v/>
       </c>
-      <c r="P20" s="7">
+      <c r="P20" s="6">
         <f>SUM(L20:N20)</f>
         <v/>
       </c>
@@ -1521,11 +1523,11 @@
       <c r="N21" s="6" t="n">
         <v>4177.76</v>
       </c>
-      <c r="O21" s="7">
+      <c r="O21" s="6">
         <f>SUM(C21:N21)</f>
         <v/>
       </c>
-      <c r="P21" s="7">
+      <c r="P21" s="6">
         <f>SUM(L21:N21)</f>
         <v/>
       </c>
@@ -1577,11 +1579,11 @@
       <c r="N22" s="6" t="n">
         <v>22069.74</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O22" s="6">
         <f>SUM(C22:N22)</f>
         <v/>
       </c>
-      <c r="P22" s="7">
+      <c r="P22" s="6">
         <f>SUM(L22:N22)</f>
         <v/>
       </c>
@@ -1633,11 +1635,11 @@
       <c r="N23" s="6" t="n">
         <v>11902.31</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O23" s="6">
         <f>SUM(C23:N23)</f>
         <v/>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="6">
         <f>SUM(L23:N23)</f>
         <v/>
       </c>
@@ -1689,11 +1691,11 @@
       <c r="N24" s="6" t="n">
         <v>43112.33</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="6">
         <f>SUM(C24:N24)</f>
         <v/>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="6">
         <f>SUM(L24:N24)</f>
         <v/>
       </c>
@@ -1745,11 +1747,11 @@
       <c r="N25" s="6" t="n">
         <v>1988.49</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="6">
         <f>SUM(C25:N25)</f>
         <v/>
       </c>
-      <c r="P25" s="7">
+      <c r="P25" s="6">
         <f>SUM(L25:N25)</f>
         <v/>
       </c>
@@ -1801,11 +1803,11 @@
       <c r="N26" s="6" t="n">
         <v>11426.95</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="6">
         <f>SUM(C26:N26)</f>
         <v/>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="6">
         <f>SUM(L26:N26)</f>
         <v/>
       </c>
@@ -1857,11 +1859,11 @@
       <c r="N27" s="6" t="n">
         <v>3579.4</v>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <f>SUM(C27:N27)</f>
         <v/>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="6">
         <f>SUM(L27:N27)</f>
         <v/>
       </c>
@@ -1913,11 +1915,11 @@
       <c r="N28" s="6" t="n">
         <v>7534.37</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="6">
         <f>SUM(C28:N28)</f>
         <v/>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="6">
         <f>SUM(L28:N28)</f>
         <v/>
       </c>
@@ -1969,11 +1971,11 @@
       <c r="N29" s="6" t="n">
         <v>4059.37</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O29" s="6">
         <f>SUM(C29:N29)</f>
         <v/>
       </c>
-      <c r="P29" s="7">
+      <c r="P29" s="6">
         <f>SUM(L29:N29)</f>
         <v/>
       </c>
@@ -2025,11 +2027,11 @@
       <c r="N30" s="6" t="n">
         <v>5884.06</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <f>SUM(C30:N30)</f>
         <v/>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="6">
         <f>SUM(L30:N30)</f>
         <v/>
       </c>
@@ -2081,11 +2083,11 @@
       <c r="N31" s="6" t="n">
         <v>9761.040000000001</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <f>SUM(C31:N31)</f>
         <v/>
       </c>
-      <c r="P31" s="7">
+      <c r="P31" s="6">
         <f>SUM(L31:N31)</f>
         <v/>
       </c>
@@ -2137,11 +2139,11 @@
       <c r="N32" s="6" t="n">
         <v>4346.55</v>
       </c>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <f>SUM(C32:N32)</f>
         <v/>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="6">
         <f>SUM(L32:N32)</f>
         <v/>
       </c>
@@ -2193,11 +2195,11 @@
       <c r="N33" s="6" t="n">
         <v>4319.15</v>
       </c>
-      <c r="O33" s="7">
+      <c r="O33" s="6">
         <f>SUM(C33:N33)</f>
         <v/>
       </c>
-      <c r="P33" s="7">
+      <c r="P33" s="6">
         <f>SUM(L33:N33)</f>
         <v/>
       </c>
@@ -2249,11 +2251,11 @@
       <c r="N34" s="6" t="n">
         <v>2403.06</v>
       </c>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <f>SUM(C34:N34)</f>
         <v/>
       </c>
-      <c r="P34" s="7">
+      <c r="P34" s="6">
         <f>SUM(L34:N34)</f>
         <v/>
       </c>
@@ -2305,11 +2307,11 @@
       <c r="N35" s="6" t="n">
         <v>1673.3</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <f>SUM(C35:N35)</f>
         <v/>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <f>SUM(L35:N35)</f>
         <v/>
       </c>
@@ -2361,22 +2363,22 @@
       <c r="N36" s="6" t="n">
         <v>942.55</v>
       </c>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <f>SUM(C36:N36)</f>
         <v/>
       </c>
-      <c r="P36" s="7">
+      <c r="P36" s="6">
         <f>SUM(L36:N36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Total Revenue (per statement)</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="9" t="n">
         <v>312566.16</v>
       </c>
@@ -2413,17 +2415,17 @@
       <c r="N37" s="9" t="n">
         <v>325964.5</v>
       </c>
-      <c r="O37" s="10">
+      <c r="O37" s="9">
         <f>SUM(C37:N37)</f>
         <v/>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="9">
         <f>SUM(L37:N37)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Monthly revenue (computed)</t>
         </is>
@@ -2433,59 +2435,59 @@
           <t>derived</t>
         </is>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
         <v/>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
         <v/>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
         <v/>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
         <v/>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
         <v/>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
         <v/>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
         <v/>
       </c>
-      <c r="J39" s="12">
+      <c r="J39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
         <v/>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
         <v/>
       </c>
-      <c r="L39" s="12">
+      <c r="L39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
         <v/>
       </c>
-      <c r="M39" s="12">
+      <c r="M39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
         <v/>
       </c>
-      <c r="N39" s="12">
+      <c r="N39" s="11">
         <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
         <v/>
       </c>
-      <c r="O39" s="12">
+      <c r="O39" s="11">
         <f>SUM(C39:N39)</f>
         <v/>
       </c>
-      <c r="P39" s="12">
+      <c r="P39" s="11">
         <f>SUM(L39:N39)</f>
         <v/>
       </c>
@@ -2577,47 +2579,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Gross Potential Rent</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A6,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A6,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>IFERROR(B6/180,"")</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <f>IFERROR(B6/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Gain/(Loss) to Lease</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A7,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A7,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <f>IFERROR(B7/180,"")</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <f>IFERROR(B7/B16,"")</f>
         <v/>
       </c>
@@ -2633,175 +2635,175 @@
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IF(SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)&lt;&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)*4,(C6+C7))</f>
+        <f>IF(SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37)&lt;&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)*4,(C6+C7))</f>
         <v/>
       </c>
       <c r="D8" s="9">
         <f>IFERROR(B8/180,"")</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f>IFERROR(B8/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A9,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A9,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <f>IFERROR(B9/180,"")</f>
         <v/>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <f>IFERROR(B9/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A10,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A10,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <f>IFERROR(B10/180,"")</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <f>IFERROR(B10/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Non-Revenue Units</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A11,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A11,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <f>IFERROR(B11/180,"")</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <f>IFERROR(B11/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Delinquency</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A12,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A12,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <f>IFERROR(B12/180,"")</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f>IFERROR(B12/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Utility Reimbursements</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A13,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A13,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <f>IFERROR(B13/180,"")</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f>IFERROR(B13/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A14,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A14,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <f>IFERROR(B14/180,"")</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>IFERROR(B14/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Revenue Adjustments</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A15,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A15,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <f>IFERROR(B15/180,"")</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f>IFERROR(B15/B16,"")</f>
         <v/>
       </c>
@@ -2824,283 +2826,283 @@
         <f>IFERROR(B16/180,"")</f>
         <v/>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <f>IFERROR(B16/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A17,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A17,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <f>IFERROR(B17/180,"")</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>IFERROR(B17/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Leasing and Marketing</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A18,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A18,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <f>IFERROR(B18/180,"")</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>IFERROR(B18/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A19,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A19,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <f>IFERROR(B19/180,"")</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="14">
         <f>IFERROR(B19/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A20,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A20,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <f>IFERROR(B20/180,"")</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="14">
         <f>IFERROR(B20/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Property Taxes</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A21,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A21,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <f>IFERROR(B21/180,"")</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <f>IFERROR(B21/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Legal and Professional</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A22,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A22,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <f>IFERROR(B22/180,"")</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="14">
         <f>IFERROR(B22/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Management Fee</t>
         </is>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A23,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A23,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <f>IFERROR(B23/180,"")</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="14">
         <f>IFERROR(B23/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Landscaping</t>
         </is>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A24,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A24,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="13">
         <f>IFERROR(B24/180,"")</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="14">
         <f>IFERROR(B24/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Repairs and Maintenance</t>
         </is>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A25,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A25,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <f>IFERROR(B25/180,"")</f>
         <v/>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="14">
         <f>IFERROR(B25/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Unit Turns</t>
         </is>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A26,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A26,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="13">
         <f>IFERROR(B26/180,"")</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="14">
         <f>IFERROR(B26/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A27,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A27,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <f>IFERROR(B27/180,"")</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <f>IFERROR(B27/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Expense Adjustments</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A28,'T-12 Data'!$O$6:$O$37)</f>
         <v/>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <f>SUMIF('T-12 Data'!$B$6:$B$37,$A28,'T-12 Data'!$P$6:$P$37)*4</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <f>IFERROR(B28/180,"")</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="14">
         <f>IFERROR(B28/B16,"")</f>
         <v/>
       </c>
@@ -3123,7 +3125,7 @@
         <f>IFERROR(B29/180,"")</f>
         <v/>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <f>IFERROR(B29/B16,"")</f>
         <v/>
       </c>
@@ -3146,7 +3148,7 @@
         <f>IFERROR(B30/180,"")</f>
         <v/>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="15">
         <f>IFERROR(B30/B16,"")</f>
         <v/>
       </c>
@@ -3159,13 +3161,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Other Income — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="17" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3250,28 +3252,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Total other income</t>
         </is>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <f>'P&amp;L Summary'!B14</f>
         <v/>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <f>'P&amp;L Summary'!C14</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Utility Reimbursements — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3330,28 +3332,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Total utility reimbursements</t>
         </is>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <f>'P&amp;L Summary'!B13</f>
         <v/>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="9">
         <f>'P&amp;L Summary'!C13</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Utilities — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -3436,16 +3438,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Total utilities</t>
         </is>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <f>'P&amp;L Summary'!B27</f>
         <v/>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <f>'P&amp;L Summary'!C27</f>
         <v/>
       </c>
@@ -3504,16 +3506,16 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Error check</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3553,22 +3555,22 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
       <c r="C7" s="6" t="n">
         <v>3814903.84</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <f>IFERROR(B7-C7,"")</f>
         <v/>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="17">
         <f>IF(C7="","NOT CHECKED",IF(ABS(D7)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3576,22 +3578,22 @@
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <f>'P&amp;L Summary'!B29</f>
         <v/>
       </c>
       <c r="C8" s="6" t="n">
         <v>1688442.2</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <f>IFERROR(B8-C8,"")</f>
         <v/>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="17">
         <f>IF(C8="","NOT CHECKED",IF(ABS(D8)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3599,22 +3601,22 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <f>'P&amp;L Summary'!B30</f>
         <v/>
       </c>
       <c r="C9" s="6" t="n">
         <v>2126461.64</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <f>IFERROR(B9-C9,"")</f>
         <v/>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="17">
         <f>IF(C9="","NOT CHECKED",IF(ABS(D9)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3622,22 +3624,22 @@
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <f>'P&amp;L Summary'!B14</f>
         <v/>
       </c>
       <c r="C10" s="6" t="n">
         <v>131904.63</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <f>IFERROR(B10-C10,"")</f>
         <v/>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="17">
         <f>IF(C10="","NOT CHECKED",IF(ABS(D10)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3645,16 +3647,16 @@
           <t>Utility Reimbursements</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <f>'P&amp;L Summary'!B13</f>
         <v/>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="6">
         <f>IFERROR(B11-C11,"")</f>
         <v/>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="17">
         <f>IF(C11="","NOT CHECKED",IF(ABS(D11)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
@@ -3670,22 +3672,22 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <f>'P&amp;L Summary'!B27</f>
         <v/>
       </c>
       <c r="C12" s="6" t="n">
         <v>263952.05</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <f>IFERROR(B12-C12,"")</f>
         <v/>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="17">
         <f>IF(C12="","NOT CHECKED",IF(ABS(D12)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3695,16 +3697,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Pricing and cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3737,7 +3739,7 @@
           <t>Total purchase price</t>
         </is>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <f>B17*B18</f>
         <v/>
       </c>
@@ -3748,7 +3750,7 @@
           <t>T-12 revenue</t>
         </is>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
@@ -3759,7 +3761,7 @@
           <t>T-12 operating expenses</t>
         </is>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <f>'P&amp;L Summary'!B29</f>
         <v/>
       </c>
@@ -3770,7 +3772,7 @@
           <t>T-12 net operating income</t>
         </is>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <f>'P&amp;L Summary'!B30</f>
         <v/>
       </c>
@@ -3781,7 +3783,7 @@
           <t>T-12 cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="19">
         <f>IFERROR(B23/B19,"")</f>
         <v/>
       </c>
@@ -3792,7 +3794,7 @@
           <t>T-3 annualized revenue</t>
         </is>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
@@ -3803,7 +3805,7 @@
           <t>T-3 annualized operating expenses</t>
         </is>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <f>'P&amp;L Summary'!C29</f>
         <v/>
       </c>
@@ -3814,7 +3816,7 @@
           <t>T-3 annualized net operating income</t>
         </is>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <f>'P&amp;L Summary'!C30</f>
         <v/>
       </c>
@@ -3825,7 +3827,7 @@
           <t>T-3 annualized cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="19">
         <f>IFERROR(B28/B19,"")</f>
         <v/>
       </c>
@@ -3871,22 +3873,22 @@
           <t>Broker pro forma cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="19">
         <f>IFERROR(B33/B19,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Revenue trend</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3894,7 +3896,7 @@
           <t>T-12 revenue</t>
         </is>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="6">
         <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
@@ -3905,7 +3907,7 @@
           <t>T-6 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <f>SUM('T-12 Data'!I39:N39)*2</f>
         <v/>
       </c>
@@ -3921,7 +3923,7 @@
           <t>T-3 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
@@ -3932,7 +3934,7 @@
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="20">
         <f>IFERROR(B39/B21-1,"")</f>
         <v/>
       </c>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -2631,11 +2631,11 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>IF(SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37)&lt;&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37),B6+B7)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$37,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37),B6+B7)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IF(SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37)&lt;&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)*4,(C6+C7))</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$37,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)*4,(C6+C7))</f>
         <v/>
       </c>
       <c r="D8" s="9">

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -2436,51 +2436,51 @@
         </is>
       </c>
       <c r="C39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
         <v/>
       </c>
       <c r="D39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
         <v/>
       </c>
       <c r="E39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
         <v/>
       </c>
       <c r="F39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
         <v/>
       </c>
       <c r="G39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
         <v/>
       </c>
       <c r="H39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
         <v/>
       </c>
       <c r="I39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
         <v/>
       </c>
       <c r="J39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
         <v/>
       </c>
       <c r="K39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
         <v/>
       </c>
       <c r="L39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
         <v/>
       </c>
       <c r="M39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
         <v/>
       </c>
       <c r="N39" s="11">
-        <f>IF(SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37)&lt;&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
         <v/>
       </c>
       <c r="O39" s="11">

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -121,16 +121,16 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fixture Park — as of 2026-06-30</t>
+          <t>505 West — as of 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -639,49 +639,49 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>MARKET RENT (1016)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>Gross Potential Rent</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
       <c r="C6" s="6" t="n">
-        <v>319842.65</v>
+        <v>476135</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>319950.56</v>
+        <v>470940</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>320383.35</v>
+        <v>433920</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>320498.47</v>
+        <v>443805</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>325401.43</v>
+        <v>433426.45</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>323898.59</v>
+        <v>432350</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>324989.92</v>
+        <v>420650</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>325437.91</v>
+        <v>443570</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>325890.7</v>
+        <v>414630</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>332749.29</v>
+        <v>419130</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>333211.68</v>
+        <v>468010</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>333678.88</v>
+        <v>441255</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(C6:N6)</f>
@@ -695,7 +695,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Loss to Lease</t>
+          <t>LOSS/GAIN TO LEASE (1017)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -704,40 +704,40 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-6656.86</v>
+        <v>-7306.8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-6671.06</v>
+        <v>-2353.76</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-6692.08</v>
+        <v>31867.97</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-6841.42</v>
+        <v>18552.61</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-6821.9</v>
+        <v>29648.52</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-6802.27</v>
+        <v>25774.48</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-6837.11</v>
+        <v>37521.06</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-6858.45</v>
+        <v>15844.3</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>-6879.89</v>
+        <v>41032.4</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>-6901.43</v>
+        <v>36170.36</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>-6923.07</v>
+        <v>-13487.99</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>-7079.81</v>
+        <v>13641.57</v>
       </c>
       <c r="O7" s="6">
         <f>SUM(C7:N7)</f>
@@ -751,7 +751,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Vacancy Loss</t>
+          <t>VACANCY (1020)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -760,40 +760,40 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-18373.24</v>
+        <v>-25553.34</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-18689.64</v>
+        <v>-34150.64</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-18653.88</v>
+        <v>-37841.85</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-18599.7</v>
+        <v>-36244.9</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-18822.95</v>
+        <v>-43894.64</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-18674.93</v>
+        <v>-38320.96</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-18677.36</v>
+        <v>-33136.74</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-19013.49</v>
+        <v>-29748.93</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-18978.89</v>
+        <v>-33607.82</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-19315.57</v>
+        <v>-31074.89</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>-19281.53</v>
+        <v>-23046.7</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>-19247.76</v>
+        <v>-17378.18</v>
       </c>
       <c r="O8" s="6">
         <f>SUM(C8:N8)</f>
@@ -807,49 +807,49 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Concessions — Move-in</t>
+          <t>MANAGEMENT OFFICE/MODEL (1030)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Concessions</t>
+          <t>Non-Revenue Units</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-3472.17</v>
+        <v>-1135</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-3546.98</v>
+        <v>-1135</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-3554.37</v>
+        <v>-1135</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-3558.27</v>
+        <v>-1135</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-3544.42</v>
+        <v>-1135</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-3530.52</v>
+        <v>-1135</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-3545.16</v>
+        <v>-1135</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-3623.71</v>
+        <v>-1135</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-3631.32</v>
+        <v>-1135</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>-3638.99</v>
+        <v>-1135</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>-3646.7</v>
+        <v>-1135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>-3654.47</v>
+        <v>-1135</v>
       </c>
       <c r="O9" s="6">
         <f>SUM(C9:N9)</f>
@@ -863,49 +863,49 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>STAFF UNITS (1040)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>Non-Revenue Units</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Non-Revenue Units</t>
-        </is>
-      </c>
       <c r="C10" s="6" t="n">
-        <v>-1277.88</v>
+        <v>-781</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-1272.63</v>
+        <v>-452</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-1293.68</v>
+        <v>-1110</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-1288.46</v>
+        <v>-431.06</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-1301.79</v>
+        <v>-329</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-1290.1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-1288.78</v>
+        <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-1309.9</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-1306.03</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>-1327.18</v>
+        <v>0</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-1323.35</v>
+        <v>0</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-1344.54</v>
+        <v>0</v>
       </c>
       <c r="O10" s="6">
         <f>SUM(C10:N10)</f>
@@ -919,49 +919,49 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Bad Debt</t>
+          <t>ONE-TIME CONCESSION (1052)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Delinquency</t>
+          <t>Concessions</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-2207.29</v>
+        <v>-13037.5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-2246.35</v>
+        <v>-1545</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-2242.69</v>
+        <v>-21962.5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-2281.81</v>
+        <v>-22037.5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-2264.63</v>
+        <v>-7345.69</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-2247.42</v>
+        <v>-1215</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-2293.37</v>
+        <v>-20850</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>-2289.82</v>
+        <v>-11027.38</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-2286.3</v>
+        <v>-727.5</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>-2327.81</v>
+        <v>-1000</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>-2324.36</v>
+        <v>-4110</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>-2320.94</v>
+        <v>-1420</v>
       </c>
       <c r="O11" s="6">
         <f>SUM(C11:N11)</f>
@@ -975,7 +975,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RUBS — Water/Sewer</t>
+          <t>VALET TRASH REIMBURSEMENTS (3001)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -984,40 +984,40 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9729</v>
+        <v>37.09</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9813.030000000001</v>
+        <v>7623.35</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>9907</v>
+        <v>7491.13</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>9991.25</v>
+        <v>7478.23</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>9829.1</v>
+        <v>7558.72</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>9863.809999999999</v>
+        <v>7488.38</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>9977.950000000001</v>
+        <v>7593.23</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>10072.39</v>
+        <v>7659.09</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>9969.969999999999</v>
+        <v>7545.77</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>10064.7</v>
+        <v>7575.75</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>10159.58</v>
+        <v>7773.02</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>10254.61</v>
+        <v>7901.86</v>
       </c>
       <c r="O12" s="6">
         <f>SUM(C12:N12)</f>
@@ -1031,49 +1031,49 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RUBS — Trash</t>
+          <t>LATE CHARGES (3011)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Utility Reimbursements</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4204</v>
+        <v>2715.13</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4223.87</v>
+        <v>5660.34</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4248</v>
+        <v>5830.2</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4267.96</v>
+        <v>4373.31</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4266.76</v>
+        <v>4465.85</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>4265.49</v>
+        <v>4141.8</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>4298.26</v>
+        <v>3555.21</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>4322.59</v>
+        <v>4499.5</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4346.99</v>
+        <v>3873.6</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>4371.44</v>
+        <v>1948.93</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>4395.96</v>
+        <v>2287.68</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>4420.55</v>
+        <v>4290.7</v>
       </c>
       <c r="O13" s="6">
         <f>SUM(C13:N13)</f>
@@ -1087,7 +1087,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Pet Rent</t>
+          <t>NSF FEE (3012)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1096,40 +1096,40 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3891.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3883.02</v>
+        <v>150</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3957.5</v>
+        <v>250</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3949.11</v>
+        <v>50</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3921.06</v>
+        <v>200</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3971.95</v>
+        <v>150</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3975.46</v>
+        <v>250</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>3971.12</v>
+        <v>-50</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>3966.85</v>
+        <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>4041.63</v>
+        <v>0</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>4037.47</v>
+        <v>100</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>4033.37</v>
+        <v>0</v>
       </c>
       <c r="O14" s="6">
         <f>SUM(C14:N14)</f>
@@ -1143,7 +1143,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>APPLICATION FEES (3030)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1152,40 +1152,40 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>3096.5</v>
+        <v>600</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3108.43</v>
+        <v>240</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3123.5</v>
+        <v>2040</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3135.5</v>
+        <v>1140</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3131.87</v>
+        <v>1140</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3128.19</v>
+        <v>1440</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>3149.65</v>
+        <v>1560</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>3164.87</v>
+        <v>1377.07</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>3180.13</v>
+        <v>1800</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>3195.45</v>
+        <v>2520</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>3210.81</v>
+        <v>2040</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>3226.21</v>
+        <v>540</v>
       </c>
       <c r="O15" s="6">
         <f>SUM(C15:N15)</f>
@@ -1199,7 +1199,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Late Fees</t>
+          <t>ADMINISTRATIVE FEE (3036)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1208,40 +1208,40 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1429.75</v>
+        <v>1800</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1454.26</v>
+        <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1451.25</v>
+        <v>3000</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1475.8</v>
+        <v>4400</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1464.04</v>
+        <v>1000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1452.25</v>
+        <v>60</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1481.22</v>
+        <v>2800</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1478.28</v>
+        <v>797.76</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1475.35</v>
+        <v>1666.97</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>1501.45</v>
+        <v>4000</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>1498.57</v>
+        <v>3035</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>1524.71</v>
+        <v>900</v>
       </c>
       <c r="O16" s="6">
         <f>SUM(C16:N16)</f>
@@ -1255,7 +1255,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Application Fees</t>
+          <t>TENANT DAMAGE REIMBURSEMENT (3040)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1264,40 +1264,40 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1179.1</v>
+        <v>14111.85</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1172.4</v>
+        <v>8236</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1189.9</v>
+        <v>4986</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1183.23</v>
+        <v>3636</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1193.61</v>
+        <v>5064</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1180.97</v>
+        <v>1553</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1200.9</v>
+        <v>145</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1195.45</v>
+        <v>4077.2</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1213.03</v>
+        <v>7386</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>1207.62</v>
+        <v>2945</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>1225.22</v>
+        <v>1521</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1242.85</v>
+        <v>5220</v>
       </c>
       <c r="O17" s="6">
         <f>SUM(C17:N17)</f>
@@ -1311,49 +1311,49 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>UTILITIES RECOVERY (3050)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Utility Reimbursements</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>763.2</v>
+        <v>387.05</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>752.61</v>
+        <v>702.58</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>757.8</v>
+        <v>446.66</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>762.23</v>
+        <v>492.3</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>762.83</v>
+        <v>762.3099999999999</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>763.42</v>
+        <v>563.4400000000001</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>770.17</v>
+        <v>401.5</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>775.39</v>
+        <v>479.06</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>780.63</v>
+        <v>645.89</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>785.87</v>
+        <v>243.33</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>791.13</v>
+        <v>551.4</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>796.39</v>
+        <v>68.58</v>
       </c>
       <c r="O18" s="6">
         <f>SUM(C18:N18)</f>
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Miscellaneous Income</t>
+          <t>FEE CONCESSION (3053)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1376,40 +1376,40 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>417.9</v>
+        <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>417.79</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>418.1</v>
+        <v>3790</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>427</v>
+        <v>-3790</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>424.78</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>422.55</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>423.73</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>433.06</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>433.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>433.74</v>
+        <v>0</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>434.1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>434.45</v>
+        <v>0</v>
       </c>
       <c r="O19" s="6">
         <f>SUM(C19:N19)</f>
@@ -1423,49 +1423,49 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>VENDING INCOME (3060)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>5193</v>
+        <v>0</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5172.36</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5262</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>5241.48</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>5194.75</v>
+        <v>114.68</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>5252.94</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>5248.28</v>
+        <v>102.97</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>5338.16</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>5323.13</v>
+        <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>5413.17</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>5398.29</v>
+        <v>0</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>5383.49</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6">
         <f>SUM(C20:N20)</f>
@@ -1479,49 +1479,49 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Locator Fees</t>
+          <t>CABLE INCOME (3066)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Leasing and Marketing</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3941</v>
+        <v>0</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4028.97</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4040</v>
+        <v>4156.56</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4047.06</v>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4033.96</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4020.8</v>
+        <v>3815.57</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>4040.06</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>4051.28</v>
+        <v>3708.35</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>4143.56</v>
+        <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4154.9</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>4166.3</v>
+        <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>4177.76</v>
+        <v>3664.94</v>
       </c>
       <c r="O21" s="6">
         <f>SUM(C21:N21)</f>
@@ -1535,49 +1535,49 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>On-site Payroll</t>
+          <t>LAUNDRY INCOME (3070)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>20734</v>
+        <v>1223.54</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>20856.34</v>
+        <v>799.13</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>21122.82</v>
+        <v>1306</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>21139.79</v>
+        <v>2138.26</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>21156.45</v>
+        <v>1492.13</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>21343.31</v>
+        <v>931.0599999999999</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>21487.97</v>
+        <v>1883.38</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>21632.94</v>
+        <v>1596.17</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>21778.22</v>
+        <v>1376.55</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>21923.82</v>
+        <v>1329.19</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>22069.74</v>
+        <v>1949.99</v>
       </c>
       <c r="O22" s="6">
         <f>SUM(C22:N22)</f>
@@ -1591,49 +1591,49 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>COURT COST REIMBURSEMENT (3080)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>11361.5</v>
+        <v>3315</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>11390.16</v>
+        <v>3134</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>11661.5</v>
+        <v>4332</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11690.42</v>
+        <v>3594</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>11661.39</v>
+        <v>2306</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>11632.17</v>
+        <v>2607</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>11696.17</v>
+        <v>5000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>11737.06</v>
+        <v>5812</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>11778.11</v>
+        <v>1989</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>11819.34</v>
+        <v>1806</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11860.74</v>
+        <v>1139</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11902.31</v>
+        <v>3734</v>
       </c>
       <c r="O23" s="6">
         <f>SUM(C23:N23)</f>
@@ -1647,49 +1647,49 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Real Estate Taxes</t>
+          <t>BAD DEBT WRITE-OFF - OTHER (3086)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes</t>
+          <t>Delinquency</t>
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>41250</v>
+        <v>-3525.75</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>41346.09</v>
+        <v>-29951.36</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>41484</v>
+        <v>-27277.24</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>41581.02</v>
+        <v>-8640.1</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>41470.39</v>
+        <v>-2248.65</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>41359.14</v>
+        <v>-19998.84</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>41581.82</v>
+        <v>-18999.39</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>41721.68</v>
+        <v>-10619.34</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>42687.17</v>
+        <v>-13403.76</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>42828.27</v>
+        <v>-25559.28</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>42969.99</v>
+        <v>-2563.26</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>43112.33</v>
+        <v>-11400.91</v>
       </c>
       <c r="O24" s="6">
         <f>SUM(C24:N24)</f>
@@ -1703,49 +1703,49 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Legal &amp; Audit</t>
+          <t>TERMINATION FEE (3112)</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Legal and Professional</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1875.5</v>
+        <v>8757.5</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1900.04</v>
+        <v>10432</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1926.5</v>
+        <v>7430</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1912.08</v>
+        <v>2750</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1927.08</v>
+        <v>17258</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1903.06</v>
+        <v>8532</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1933.43</v>
+        <v>875.65</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>1959.98</v>
+        <v>18553.5</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1947.57</v>
+        <v>9650</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>1974.18</v>
+        <v>9946</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>1961.82</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>1988.49</v>
+        <v>10442</v>
       </c>
       <c r="O25" s="6">
         <f>SUM(C25:N25)</f>
@@ -1759,49 +1759,49 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>CONCIERGE SERVICES INCOME (3117)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>10759.5</v>
+        <v>1564.64</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>10860.47</v>
+        <v>1520.45</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10972.5</v>
+        <v>1508.23</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>11073.71</v>
+        <v>1505.65</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>10900.99</v>
+        <v>1485.46</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>10947.1</v>
+        <v>1497.66</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>11081.56</v>
+        <v>1518.64</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>11194.11</v>
+        <v>1526.67</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>11087.83</v>
+        <v>1509.16</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>11200.7</v>
+        <v>1515.13</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>11313.74</v>
+        <v>1554.6</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>11426.95</v>
+        <v>1580.35</v>
       </c>
       <c r="O26" s="6">
         <f>SUM(C26:N26)</f>
@@ -1815,49 +1815,49 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Landscaping &amp; Grounds</t>
+          <t>PET FEES (3118)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>3384</v>
+        <v>1200</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3364.27</v>
+        <v>-400</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3417</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3466.35</v>
+        <v>400</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3429.57</v>
+        <v>2000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3461.73</v>
+        <v>1200</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>3452.45</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3505.34</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>3489.28</v>
+        <v>400</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>3542.26</v>
+        <v>1200</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>3526.3</v>
+        <v>800</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>3579.4</v>
+        <v>-400</v>
       </c>
       <c r="O27" s="6">
         <f>SUM(C27:N27)</f>
@@ -1871,49 +1871,49 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>R&amp;M — Interior</t>
+          <t>PET RENT (3119)</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>7216</v>
+        <v>2007.67</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7179.35</v>
+        <v>2119.36</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7295</v>
+        <v>1989.87</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7258.51</v>
+        <v>1933.54</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>7330.73</v>
+        <v>2207.94</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>7257.84</v>
+        <v>2109.62</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>7243.31</v>
+        <v>2115.48</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>7359.3</v>
+        <v>1985.1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>7330.41</v>
+        <v>1956.77</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>7446.62</v>
+        <v>2015.4</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>7417.94</v>
+        <v>1976.2</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>7534.37</v>
+        <v>2167.74</v>
       </c>
       <c r="O28" s="6">
         <f>SUM(C28:N28)</f>
@@ -1927,49 +1927,49 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>R&amp;M — Exterior</t>
+          <t>PEST CONTROL FEES (3121)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>3917.5</v>
+        <v>604.77</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3909.02</v>
+        <v>624.3099999999999</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3904.5</v>
+        <v>623.22</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3975.11</v>
+        <v>609.41</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>3947.06</v>
+        <v>466.18</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3918.95</v>
+        <v>587.72</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4001.46</v>
+        <v>600.84</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3997.12</v>
+        <v>639.28</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>3992.85</v>
+        <v>616.3099999999999</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>3988.63</v>
+        <v>606.9400000000001</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>4063.47</v>
+        <v>597.27</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>4059.37</v>
+        <v>619.1</v>
       </c>
       <c r="O29" s="6">
         <f>SUM(C29:N29)</f>
@@ -1983,49 +1983,49 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Unit Turns</t>
+          <t>DEPOSIT WAIVER INCOME (3156)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Unit Turns</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>5552</v>
+        <v>3528.17</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5572.16</v>
+        <v>2769.72</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>5598</v>
+        <v>2198.37</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>5618.28</v>
+        <v>1663.81</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5610.34</v>
+        <v>1206.3</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>5602.32</v>
+        <v>987.22</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>5639.68</v>
+        <v>882.9</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>5665.79</v>
+        <v>686.48</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>5804.98</v>
+        <v>482.11</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>5831.26</v>
+        <v>344.53</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>5857.62</v>
+        <v>340</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>5884.06</v>
+        <v>340</v>
       </c>
       <c r="O30" s="6">
         <f>SUM(C30:N30)</f>
@@ -2039,49 +2039,49 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Water/Sewer</t>
+          <t>DEPOSIT WAIVER EXPENSE (3157)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>9260</v>
+        <v>-2271.88</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>9426.23</v>
+        <v>-1692.24</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>9413</v>
+        <v>-1092.33</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>9579.440000000001</v>
+        <v>-531.79</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>9509.51</v>
+        <v>-233.94</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>9439.43</v>
+        <v>-6.17</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>9634.540000000001</v>
+        <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>9621.76</v>
+        <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>9609.120000000001</v>
+        <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>9785.610000000001</v>
+        <v>0</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>9773.25</v>
+        <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>9761.040000000001</v>
+        <v>0</v>
       </c>
       <c r="O31" s="6">
         <f>SUM(C31:N31)</f>
@@ -2095,49 +2095,49 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Electric (common)</t>
+          <t>RENTER'S INSURANCE INCOME (3175)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>4215</v>
+        <v>4748.18</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4234.87</v>
+        <v>4638.37</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>4259</v>
+        <v>4510.04</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>4278.96</v>
+        <v>4444.8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>4277.76</v>
+        <v>4732.89</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>4276.49</v>
+        <v>4964.74</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>4309.26</v>
+        <v>4773.04</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>4248.59</v>
+        <v>4827.85</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>4272.99</v>
+        <v>4762.84</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>4297.44</v>
+        <v>4845.33</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>4321.96</v>
+        <v>4970.37</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>4346.55</v>
+        <v>5144.86</v>
       </c>
       <c r="O32" s="6">
         <f>SUM(C32:N32)</f>
@@ -2151,49 +2151,49 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Trash</t>
+          <t>RENTER'S INSURANCE EXPENSE (3176)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>4100.5</v>
+        <v>-4257.41</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>4097.92</v>
+        <v>-4244.79</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>4099.5</v>
+        <v>-4121.98</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>4180.01</v>
+        <v>-4020.74</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4156.86</v>
+        <v>-4050.07</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>4133.64</v>
+        <v>-4081.05</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>4143.66</v>
+        <v>-4081.05</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4228.44</v>
+        <v>-4720.33</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>4230.27</v>
+        <v>-4253.73</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>4232.17</v>
+        <v>-4172.95</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>4234.13</v>
+        <v>-4377.02</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>4319.15</v>
+        <v>-4429.17</v>
       </c>
       <c r="O33" s="6">
         <f>SUM(C33:N33)</f>
@@ -2207,49 +2207,49 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Gas</t>
+          <t>TRANSFER FEE (3179)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>2300.5</v>
+        <v>750</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2292.83</v>
+        <v>500</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2334.5</v>
+        <v>250</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2326.88</v>
+        <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>2307.68</v>
+        <v>-250</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2335.43</v>
+        <v>250</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2334.83</v>
+        <v>250</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2329.61</v>
+        <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2371.42</v>
+        <v>500</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>2366.27</v>
+        <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>2408.15</v>
+        <v>0</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>2403.06</v>
+        <v>0</v>
       </c>
       <c r="O34" s="6">
         <f>SUM(C34:N34)</f>
@@ -2263,49 +2263,49 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Cable/Internet</t>
+          <t>MISCELLANEOUS INCOME (3180)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1584</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1601.19</v>
+        <v>-55.69</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1604.22</v>
+        <v>5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1613.38</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1622.52</v>
+        <v>658</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1611.62</v>
+        <v>1000</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1630.51</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1649.42</v>
+        <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1668.36</v>
+        <v>169</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>1654.32</v>
+        <v>99.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1673.3</v>
+        <v>1000</v>
       </c>
       <c r="O35" s="6">
         <f>SUM(C35:N35)</f>
@@ -2319,49 +2319,49 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Expense Adjustments</t>
+          <t>UTILITY FEE REIMBURSEMENT (3183)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Expense Adjustments</t>
+          <t>Utility Reimbursements</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>889.5</v>
+        <v>1121.8</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>899.54</v>
+        <v>1128.9</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>910.5</v>
+        <v>1118.25</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>901.5599999999999</v>
+        <v>1086.3</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>907.09</v>
+        <v>1100.5</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>912.6</v>
+        <v>1075.65</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>906.41</v>
+        <v>1079.2</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>917.41</v>
+        <v>1153.75</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>928.4299999999999</v>
+        <v>1111.15</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>920.45</v>
+        <v>1093.4</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>931.49</v>
+        <v>1079.2</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>942.55</v>
+        <v>1107.6</v>
       </c>
       <c r="O36" s="6">
         <f>SUM(C36:N36)</f>
@@ -2373,127 +2373,5619 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Total Revenue (per statement)</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="n">
-        <v>312566.16</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>312349.31</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>312999.7</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>313120.89</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>317639.79</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>316401.98</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>317625.48</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>317755.69</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>318174.62</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>324840.21</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>325465.51</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>325964.5</v>
-      </c>
-      <c r="O37" s="9">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>WATER/SEWER REIMBURSEMENT (3186)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Utility Reimbursements</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>16099.6</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>17180.46</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>18780.45</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>16826.4</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>16462.81</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>12355.23</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>16192.16</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>15956.69</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>15101.96</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>14566.56</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>15246.49</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>16100.07</v>
+      </c>
+      <c r="O37" s="6">
         <f>SUM(C37:N37)</f>
         <v/>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="6">
         <f>SUM(L37:N37)</f>
         <v/>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>TRASH REIMBURSEMENT (3187)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Utility Reimbursements</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>10534.64</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>2946.36</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>3103.34</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>3097.01</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>3130.81</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>2988.02</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>3068.14</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>3203.76</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>3150.47</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>3083.46</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>3046.86</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>3175.27</v>
+      </c>
+      <c r="O38" s="6">
+        <f>SUM(C38:N38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="6">
+        <f>SUM(L38:N38)</f>
+        <v/>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>SALES TAX COLLECTED (3192)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>-90.08</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O39" s="6">
+        <f>SUM(C39:N39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="6">
+        <f>SUM(L39:N39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>OTHER REIMBURSEMENTS (3198)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Utility Reimbursements</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>-175</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="6">
+        <f>SUM(C40:N40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="6">
+        <f>SUM(L40:N40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT DEPOSIT WAIVER FEE (3081)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>970.62</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>1490.85</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>1858.88</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>2223.43</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>2302.09</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>2531</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>2519.86</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>2519.05</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>2557.33</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>2448</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>2369.83</v>
+      </c>
+      <c r="O41" s="6">
+        <f>SUM(C41:N41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="6">
+        <f>SUM(L41:N41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT WRITE-OFF (3084)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>-336.72</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>-10286.8</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>-8881.82</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>-1188.12</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>-870.84</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>-8098.69</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>-13790.59</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>-4600.04</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>-15090.62</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>-2067.98</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>-294.2</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>-4061.39</v>
+      </c>
+      <c r="O42" s="6">
+        <f>SUM(C42:N42)</f>
+        <v/>
+      </c>
+      <c r="P42" s="6">
+        <f>SUM(L42:N42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT- ALLOWANCE FOR DOUBTFUL ACCOUNTS (3085)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>-2314.75</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2081.69</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>-1130.84</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>-6768.39</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>-1645.85</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>7741.84</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>-399.66</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>2268.21</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>174.34</v>
+      </c>
+      <c r="O43" s="6">
+        <f>SUM(C43:N43)</f>
+        <v/>
+      </c>
+      <c r="P43" s="6">
+        <f>SUM(L43:N43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT COLLECTED - DEPOSIT ALTERNATIVE CLAIMS (3087)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>7371.28</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>14086.19</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>10823.11</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>3913.02</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>6606.56</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1412.32</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>7476.17</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>1536.83</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="6">
+        <f>SUM(C44:N44)</f>
+        <v/>
+      </c>
+      <c r="P44" s="6">
+        <f>SUM(L44:N44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT COLLECTED - IN HOUSE (3088)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>2703.89</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>-77.75</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>-582.25</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6">
+        <f>SUM(C45:N45)</f>
+        <v/>
+      </c>
+      <c r="P45" s="6">
+        <f>SUM(L45:N45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT COLLECTED - COLLECTION AGENCY (3089)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>459.74</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>618.1900000000001</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="O46" s="6">
+        <f>SUM(C46:N46)</f>
+        <v/>
+      </c>
+      <c r="P46" s="6">
+        <f>SUM(L46:N46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>BAD DEBT ADJUSTMENTS (3091)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Delinquency</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>1775.49</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>-268.6</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>-402.66</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1917.15</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>1396.6</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>-15.47</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>829.16</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1096.75</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>-122.35</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>-363.07</v>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>-386.3</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>1926.06</v>
+      </c>
+      <c r="O47" s="6">
+        <f>SUM(C47:N47)</f>
+        <v/>
+      </c>
+      <c r="P47" s="6">
+        <f>SUM(L47:N47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>PROMOTIONAL MATERIALS (5010)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>156.43</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>156.68</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>60.83</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="O48" s="6">
+        <f>SUM(C48:N48)</f>
+        <v/>
+      </c>
+      <c r="P48" s="6">
+        <f>SUM(L48:N48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>MARKETING COLLATERAL (5020)</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>589.55</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6">
+        <f>SUM(C49:N49)</f>
+        <v/>
+      </c>
+      <c r="P49" s="6">
+        <f>SUM(L49:N49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>ONLINE ADVERTISING (5070)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>8164.67</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>6229.07</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>5675.06</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>6204.47</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>4939.9</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>5926.66</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>6068.55</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>4562.86</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>4345.64</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>6279.75</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>5084.74</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>5222.28</v>
+      </c>
+      <c r="O50" s="6">
+        <f>SUM(C50:N50)</f>
+        <v/>
+      </c>
+      <c r="P50" s="6">
+        <f>SUM(L50:N50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>SPECIALTY MARKETING (5090)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>1382</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>179.72</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="O51" s="6">
+        <f>SUM(C51:N51)</f>
+        <v/>
+      </c>
+      <c r="P51" s="6">
+        <f>SUM(L51:N51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>MARKETING PERFORMANCE MEASUREMENT (MPM) &amp; LEAD MGM (5099)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>526.42</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>526.42</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>526.42</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>854.42</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>1268.2</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>2058.5</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>509.08</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>560.42</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>534.63</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>534.63</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>534.63</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>534.63</v>
+      </c>
+      <c r="O52" s="6">
+        <f>SUM(C52:N52)</f>
+        <v/>
+      </c>
+      <c r="P52" s="6">
+        <f>SUM(L52:N52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>COMMUNITY FUNCTIONS (5120)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>463.88</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>231.64</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>257.03</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>283.85</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="L53" s="6" t="n">
+        <v>507.05</v>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="O53" s="6">
+        <f>SUM(C53:N53)</f>
+        <v/>
+      </c>
+      <c r="P53" s="6">
+        <f>SUM(L53:N53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>TENANT REFERRAL FEES (5160)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Leasing and Marketing</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6">
+        <f>SUM(C54:N54)</f>
+        <v/>
+      </c>
+      <c r="P54" s="6">
+        <f>SUM(L54:N54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>OFFICE SUPPLIES (5410)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>241.51</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>232.96</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>114.72</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>339.21</v>
+      </c>
+      <c r="O55" s="6">
+        <f>SUM(C55:N55)</f>
+        <v/>
+      </c>
+      <c r="P55" s="6">
+        <f>SUM(L55:N55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>TRAINING/SEMINARS (5430)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>161.75</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>161.75</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>161.75</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>161.75</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>-111.79</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>447.97</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>414.77</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="O56" s="6">
+        <f>SUM(C56:N56)</f>
+        <v/>
+      </c>
+      <c r="P56" s="6">
+        <f>SUM(L56:N56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>OFFICE EQUIP/LEASE/PURCHASE (5440)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>219.37</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6">
+        <f>SUM(C57:N57)</f>
+        <v/>
+      </c>
+      <c r="P57" s="6">
+        <f>SUM(L57:N57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>CAREER APPAREL (5455)</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>442.14</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>506.28</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6">
+        <f>SUM(C58:N58)</f>
+        <v/>
+      </c>
+      <c r="P58" s="6">
+        <f>SUM(L58:N58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TRAVEL (5460)</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>492.29</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>294.81</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>254.77</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>2427.42</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>288.35</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="O59" s="6">
+        <f>SUM(C59:N59)</f>
+        <v/>
+      </c>
+      <c r="P59" s="6">
+        <f>SUM(L59:N59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>DUES/SUBSCRIPTIONS (5470)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1703</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>551.25</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>3419.45</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="O60" s="6">
+        <f>SUM(C60:N60)</f>
+        <v/>
+      </c>
+      <c r="P60" s="6">
+        <f>SUM(L60:N60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>BLUE MOON LICENSE (5475)</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>-1603</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="6">
+        <f>SUM(C61:N61)</f>
+        <v/>
+      </c>
+      <c r="P61" s="6">
+        <f>SUM(L61:N61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>CREDIT REPORTS (5480)</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>3468</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>1938</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>867</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>1326</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>2397</v>
+      </c>
+      <c r="N62" s="6" t="n">
+        <v>969</v>
+      </c>
+      <c r="O62" s="6">
+        <f>SUM(C62:N62)</f>
+        <v/>
+      </c>
+      <c r="P62" s="6">
+        <f>SUM(L62:N62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>LEGAL EXPENSE (5510)</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Legal and Professional</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>5603.52</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1769</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>2292</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>5255.5</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>1775</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>5184.5</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>3813</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>907</v>
+      </c>
+      <c r="M63" s="6" t="n">
+        <v>1321</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>1392.25</v>
+      </c>
+      <c r="O63" s="6">
+        <f>SUM(C63:N63)</f>
+        <v/>
+      </c>
+      <c r="P63" s="6">
+        <f>SUM(L63:N63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>MRI FEES (5515)</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>702.41</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>702.4</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>702.4</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>702.4</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>702.28</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>705.35</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>705.35</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>705.35</v>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>2013.17</v>
+      </c>
+      <c r="L64" s="6" t="n">
+        <v>1358.22</v>
+      </c>
+      <c r="M64" s="6" t="n">
+        <v>1353.74</v>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>1356.68</v>
+      </c>
+      <c r="O64" s="6">
+        <f>SUM(C64:N64)</f>
+        <v/>
+      </c>
+      <c r="P64" s="6">
+        <f>SUM(L64:N64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>LRO FEES (5525)</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>570.47</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="L65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="M65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="N65" s="6" t="n">
+        <v>570.46</v>
+      </c>
+      <c r="O65" s="6">
+        <f>SUM(C65:N65)</f>
+        <v/>
+      </c>
+      <c r="P65" s="6">
+        <f>SUM(L65:N65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>TELEPHONE - LOCAL LINES (5530)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1236.68</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>493.53</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>552.6900000000001</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>512.86</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>434.01</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>453.62</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>475.64</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>1358.32</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>-340.61</v>
+      </c>
+      <c r="L66" s="6" t="n">
+        <v>1235.85</v>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>421.23</v>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>480.49</v>
+      </c>
+      <c r="O66" s="6">
+        <f>SUM(C66:N66)</f>
+        <v/>
+      </c>
+      <c r="P66" s="6">
+        <f>SUM(L66:N66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>HIGH SPEED INTERNET (5531)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>1643.92</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>1483.09</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>1550.23</v>
+      </c>
+      <c r="L67" s="6" t="n">
+        <v>737.9400000000001</v>
+      </c>
+      <c r="M67" s="6" t="n">
+        <v>795.51</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>757.6900000000001</v>
+      </c>
+      <c r="O67" s="6">
+        <f>SUM(C67:N67)</f>
+        <v/>
+      </c>
+      <c r="P67" s="6">
+        <f>SUM(L67:N67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>ANSWERING SERVICE (5535)</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>162.91</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>162.92</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>-162.92</v>
+      </c>
+      <c r="L68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="6">
+        <f>SUM(C68:N68)</f>
+        <v/>
+      </c>
+      <c r="P68" s="6">
+        <f>SUM(L68:N68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>MISCELLANEOUS (5550)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="6">
+        <f>SUM(C69:N69)</f>
+        <v/>
+      </c>
+      <c r="P69" s="6">
+        <f>SUM(L69:N69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>TECHNOLOGY COSTS (5590)</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>2872.8</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>2482.93</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>2120.92</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>2927.95</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>3122.99</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>3193.92</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>3561.85</v>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>3244.63</v>
+      </c>
+      <c r="K70" s="6" t="n">
+        <v>2079.42</v>
+      </c>
+      <c r="L70" s="6" t="n">
+        <v>3100.99</v>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>2732.74</v>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>2443.34</v>
+      </c>
+      <c r="O70" s="6">
+        <f>SUM(C70:N70)</f>
+        <v/>
+      </c>
+      <c r="P70" s="6">
+        <f>SUM(L70:N70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>MANAGEMENT FEES (5700)</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>13371.85</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>13093.02</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>12989.97</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>12456.21</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>13035.61</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>12382.67</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>12794.73</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>13280.33</v>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>13199.06</v>
+      </c>
+      <c r="L71" s="6" t="n">
+        <v>12587.18</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>13097.58</v>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>13175.35</v>
+      </c>
+      <c r="O71" s="6">
+        <f>SUM(C71:N71)</f>
+        <v/>
+      </c>
+      <c r="P71" s="6">
+        <f>SUM(L71:N71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>MANAGEMENT FEE - OTHER (5740)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="M72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="N72" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="O72" s="6">
+        <f>SUM(C72:N72)</f>
+        <v/>
+      </c>
+      <c r="P72" s="6">
+        <f>SUM(L72:N72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>PROPERTY MANAGER/ADMINISTRATOR (5810)</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>9034.41</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>5261.21</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>743.6799999999999</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>743.6799999999999</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>1007.13</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>16863.39</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>7576.57</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>7985.16</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>8554.85</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>8154.55</v>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>14041.18</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>8240.83</v>
+      </c>
+      <c r="O73" s="6">
+        <f>SUM(C73:N73)</f>
+        <v/>
+      </c>
+      <c r="P73" s="6">
+        <f>SUM(L73:N73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>OFFICE OVERTIME (5815)</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>123.26</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>294.56</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>234.23</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>786.79</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>682.49</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>258.96</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>592.25</v>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>457.89</v>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>154.22</v>
+      </c>
+      <c r="O74" s="6">
+        <f>SUM(C74:N74)</f>
+        <v/>
+      </c>
+      <c r="P74" s="6">
+        <f>SUM(L74:N74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>ASSISTANT MGR/LEASING AGENT (5820)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>11044.62</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>11139.84</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>11178.94</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>11292.14</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>10732.31</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>17006.41</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>11305.46</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>10555.13</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>11004.93</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>11226.66</v>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>14216.29</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>8715.75</v>
+      </c>
+      <c r="O75" s="6">
+        <f>SUM(C75:N75)</f>
+        <v/>
+      </c>
+      <c r="P75" s="6">
+        <f>SUM(L75:N75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>MAINTENANCE/ENGINEER/SUPERVISOR (5830)</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>6835.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>6811.23</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>6330.1</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>6997.97</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>6299.6</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>6498.7</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>333.96</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>166.97</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>2638.46</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>6368.06</v>
+      </c>
+      <c r="M76" s="6" t="n">
+        <v>9569.84</v>
+      </c>
+      <c r="N76" s="6" t="n">
+        <v>6040.82</v>
+      </c>
+      <c r="O76" s="6">
+        <f>SUM(C76:N76)</f>
+        <v/>
+      </c>
+      <c r="P76" s="6">
+        <f>SUM(L76:N76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>MAINTENANCE OVERTIME (5835)</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>4278</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>3727.3</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>2699.98</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>3121.5</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>5473.3</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>1402.85</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>799.4299999999999</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>634.6900000000001</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>1637.58</v>
+      </c>
+      <c r="L77" s="6" t="n">
+        <v>893.15</v>
+      </c>
+      <c r="M77" s="6" t="n">
+        <v>3978.17</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <v>2772.09</v>
+      </c>
+      <c r="O77" s="6">
+        <f>SUM(C77:N77)</f>
+        <v/>
+      </c>
+      <c r="P77" s="6">
+        <f>SUM(L77:N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>MAINTENANCE PAYROLL (5840)</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>9214.65</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>8664.969999999999</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>7810.81</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>6975.32</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>4535.58</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>13812.61</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>8520.9</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>8756.23</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>8718.48</v>
+      </c>
+      <c r="L78" s="6" t="n">
+        <v>8875.98</v>
+      </c>
+      <c r="M78" s="6" t="n">
+        <v>12872.46</v>
+      </c>
+      <c r="N78" s="6" t="n">
+        <v>8799.84</v>
+      </c>
+      <c r="O78" s="6">
+        <f>SUM(C78:N78)</f>
+        <v/>
+      </c>
+      <c r="P78" s="6">
+        <f>SUM(L78:N78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TEMPORARY EMPLOYMENT (5855)</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>2281.28</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>264.56</v>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="O79" s="6">
+        <f>SUM(C79:N79)</f>
+        <v/>
+      </c>
+      <c r="P79" s="6">
+        <f>SUM(L79:N79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>LEASING BONUSES (5860)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>6297.34</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>7143.34</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>5911.97</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>4482.74</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>6128.29</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>3140.74</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>3299.02</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>3985.88</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>5737.44</v>
+      </c>
+      <c r="L80" s="6" t="n">
+        <v>5051.32</v>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>4762.48</v>
+      </c>
+      <c r="N80" s="6" t="n">
+        <v>6726.2</v>
+      </c>
+      <c r="O80" s="6">
+        <f>SUM(C80:N80)</f>
+        <v/>
+      </c>
+      <c r="P80" s="6">
+        <f>SUM(L80:N80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>FRINGE BENEFITS (5870)</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>4484.84</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>4684.04</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>3279.39</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>3540.63</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>3574.6</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>4705.68</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>2834.84</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>4164.48</v>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>4377.93</v>
+      </c>
+      <c r="M81" s="6" t="n">
+        <v>6531.31</v>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>4365.09</v>
+      </c>
+      <c r="O81" s="6">
+        <f>SUM(C81:N81)</f>
+        <v/>
+      </c>
+      <c r="P81" s="6">
+        <f>SUM(L81:N81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>WORKERS COMP INSURANCE (5875)</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>1133.97</v>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>1091.63</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>940.34</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>834.28</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>869.01</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>929.73</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>477.9</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>481.13</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>624.11</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>720.13</v>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>1106.07</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>769.95</v>
+      </c>
+      <c r="O82" s="6">
+        <f>SUM(C82:N82)</f>
+        <v/>
+      </c>
+      <c r="P82" s="6">
+        <f>SUM(L82:N82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>PAYROLL TAXES (5880)</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>3506.02</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>3208.82</v>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>2598.54</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>2211.07</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>2482.36</v>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>4427.53</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>2592.59</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>2949.57</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>2919.28</v>
+      </c>
+      <c r="L83" s="6" t="n">
+        <v>3108.84</v>
+      </c>
+      <c r="M83" s="6" t="n">
+        <v>4437.68</v>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>3078.29</v>
+      </c>
+      <c r="O83" s="6">
+        <f>SUM(C83:N83)</f>
+        <v/>
+      </c>
+      <c r="P83" s="6">
+        <f>SUM(L83:N83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>RECRUITING EXPENSE (5882)</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>230.21</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>140.52</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="6">
+        <f>SUM(C84:N84)</f>
+        <v/>
+      </c>
+      <c r="P84" s="6">
+        <f>SUM(L84:N84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>PAYROLL PROCESSING (5885)</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>349.67</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>251.77</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>-41.93</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>270.96</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>527.5599999999999</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>260.72</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>291.29</v>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>268.55</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>257.22</v>
+      </c>
+      <c r="O85" s="6">
+        <f>SUM(C85:N85)</f>
+        <v/>
+      </c>
+      <c r="P85" s="6">
+        <f>SUM(L85:N85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>GROUNDS (6010)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>4995.04</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>5645.11</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>7475.27</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>4995.03</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>3803.18</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>9527.129999999999</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>6322.92</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>5544.5</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>4995</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>4995</v>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>4610.76</v>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>5054.78</v>
+      </c>
+      <c r="O86" s="6">
+        <f>SUM(C86:N86)</f>
+        <v/>
+      </c>
+      <c r="P86" s="6">
+        <f>SUM(L86:N86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>SECURITY (6030)</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>1724.36</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>1108.52</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>1724.36</v>
+      </c>
+      <c r="L87" s="6" t="n">
+        <v>1724.36</v>
+      </c>
+      <c r="M87" s="6" t="n">
+        <v>1724.36</v>
+      </c>
+      <c r="N87" s="6" t="n">
+        <v>1724.36</v>
+      </c>
+      <c r="O87" s="6">
+        <f>SUM(C87:N87)</f>
+        <v/>
+      </c>
+      <c r="P87" s="6">
+        <f>SUM(L87:N87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>SECURITY SYSTEM ACCESS MONITORING (6031)</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>283.58</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>256.79</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="L88" s="6" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="M88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="N88" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="O88" s="6">
+        <f>SUM(C88:N88)</f>
+        <v/>
+      </c>
+      <c r="P88" s="6">
+        <f>SUM(L88:N88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>FIRE PUMP TESTING (6035)</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>1315</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="6" t="n">
+        <v>1103.24</v>
+      </c>
+      <c r="N89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="6">
+        <f>SUM(C89:N89)</f>
+        <v/>
+      </c>
+      <c r="P89" s="6">
+        <f>SUM(L89:N89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>CLEANING - COMMON (6040)</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>455</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>415</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>1405</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>264.56</v>
+      </c>
+      <c r="L90" s="6" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="M90" s="6" t="n">
+        <v>817.35</v>
+      </c>
+      <c r="N90" s="6" t="n">
+        <v>915.75</v>
+      </c>
+      <c r="O90" s="6">
+        <f>SUM(C90:N90)</f>
+        <v/>
+      </c>
+      <c r="P90" s="6">
+        <f>SUM(L90:N90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>UNIT CLEANS - TURN (6041)</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Unit Turns</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>2610</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>1915</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>5610</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>1577.5</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>3365</v>
+      </c>
+      <c r="L91" s="6" t="n">
+        <v>3495</v>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>2515.01</v>
+      </c>
+      <c r="N91" s="6" t="n">
+        <v>3315</v>
+      </c>
+      <c r="O91" s="6">
+        <f>SUM(C91:N91)</f>
+        <v/>
+      </c>
+      <c r="P91" s="6">
+        <f>SUM(L91:N91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>PLUMBING (6060)</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>1908</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>2963</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>8048</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>4594.95</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>3286.9</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>1302</v>
+      </c>
+      <c r="L92" s="6" t="n">
+        <v>1472</v>
+      </c>
+      <c r="M92" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="N92" s="6" t="n">
+        <v>2655</v>
+      </c>
+      <c r="O92" s="6">
+        <f>SUM(C92:N92)</f>
+        <v/>
+      </c>
+      <c r="P92" s="6">
+        <f>SUM(L92:N92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>ELECTRICAL (6070)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>1495</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>5310</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>689</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>440.41</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>389</v>
+      </c>
+      <c r="L93" s="6" t="n">
+        <v>2945</v>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="N93" s="6" t="n">
+        <v>1525</v>
+      </c>
+      <c r="O93" s="6">
+        <f>SUM(C93:N93)</f>
+        <v/>
+      </c>
+      <c r="P93" s="6">
+        <f>SUM(L93:N93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>BUILDING EXTERIORS (6100)</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>937.5599999999999</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>5057</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>1651</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="N94" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="O94" s="6">
+        <f>SUM(C94:N94)</f>
+        <v/>
+      </c>
+      <c r="P94" s="6">
+        <f>SUM(L94:N94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>R&amp;M PRESSURE WASHING (6105)</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>657</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="6">
+        <f>SUM(C95:N95)</f>
+        <v/>
+      </c>
+      <c r="P95" s="6">
+        <f>SUM(L95:N95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>ROOF (6130)</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>825</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="6">
+        <f>SUM(C96:N96)</f>
+        <v/>
+      </c>
+      <c r="P96" s="6">
+        <f>SUM(L96:N96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>GLASS (6140)</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>484.26</v>
+      </c>
+      <c r="K97" s="6" t="n">
+        <v>555</v>
+      </c>
+      <c r="L97" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>276</v>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="6">
+        <f>SUM(C97:N97)</f>
+        <v/>
+      </c>
+      <c r="P97" s="6">
+        <f>SUM(L97:N97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CARPET REPAIR/CLEANING - TURN (6160)</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Unit Turns</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>1225</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>855</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>7919.66</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>533.47</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="K98" s="6" t="n">
+        <v>1090</v>
+      </c>
+      <c r="L98" s="6" t="n">
+        <v>1655</v>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>2125</v>
+      </c>
+      <c r="N98" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="O98" s="6">
+        <f>SUM(C98:N98)</f>
+        <v/>
+      </c>
+      <c r="P98" s="6">
+        <f>SUM(L98:N98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CARPET REPAIR/CLEANING - OCCUPIED (6161)</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>665.04</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O99" s="6">
+        <f>SUM(C99:N99)</f>
+        <v/>
+      </c>
+      <c r="P99" s="6">
+        <f>SUM(L99:N99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>EXTERMINATING CONTRACT (6190)</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>2313.44</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>3118.44</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>4533.92</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>6766.66</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>2625.37</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>1758.44</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>988</v>
+      </c>
+      <c r="K100" s="6" t="n">
+        <v>999.0599999999999</v>
+      </c>
+      <c r="L100" s="6" t="n">
+        <v>1786.39</v>
+      </c>
+      <c r="M100" s="6" t="n">
+        <v>1670.45</v>
+      </c>
+      <c r="N100" s="6" t="n">
+        <v>2766.34</v>
+      </c>
+      <c r="O100" s="6">
+        <f>SUM(C100:N100)</f>
+        <v/>
+      </c>
+      <c r="P100" s="6">
+        <f>SUM(L100:N100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>INTERIOR PAINT - TURN (6200)</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Unit Turns</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>4340</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>4095</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>2885</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>6180</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>4530</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>1440</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>3004</v>
+      </c>
+      <c r="K101" s="6" t="n">
+        <v>5560.4</v>
+      </c>
+      <c r="L101" s="6" t="n">
+        <v>5874.03</v>
+      </c>
+      <c r="M101" s="6" t="n">
+        <v>2546</v>
+      </c>
+      <c r="N101" s="6" t="n">
+        <v>2940.02</v>
+      </c>
+      <c r="O101" s="6">
+        <f>SUM(C101:N101)</f>
+        <v/>
+      </c>
+      <c r="P101" s="6">
+        <f>SUM(L101:N101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>HVAC REPAIRS (6220)</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>4117.9</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>4149</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>2716.31</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>843</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>2107</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>5298</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>1676</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>1927.48</v>
+      </c>
+      <c r="K102" s="6" t="n">
+        <v>-871</v>
+      </c>
+      <c r="L102" s="6" t="n">
+        <v>723</v>
+      </c>
+      <c r="M102" s="6" t="n">
+        <v>1530</v>
+      </c>
+      <c r="N102" s="6" t="n">
+        <v>2525</v>
+      </c>
+      <c r="O102" s="6">
+        <f>SUM(C102:N102)</f>
+        <v/>
+      </c>
+      <c r="P102" s="6">
+        <f>SUM(L102:N102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>EQUIPMENT REPAIRS (6290)</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>3268.9</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>1324.77</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>818.53</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>1375.15</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>-1375.15</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="6" t="n">
+        <v>3115.76</v>
+      </c>
+      <c r="L103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="6" t="n">
+        <v>1930.61</v>
+      </c>
+      <c r="N103" s="6" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="O103" s="6">
+        <f>SUM(C103:N103)</f>
+        <v/>
+      </c>
+      <c r="P103" s="6">
+        <f>SUM(L103:N103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>UNIT TURNS (6300)</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Unit Turns</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>4822.06</v>
+      </c>
+      <c r="K104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="6">
+        <f>SUM(C104:N104)</f>
+        <v/>
+      </c>
+      <c r="P104" s="6">
+        <f>SUM(L104:N104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>LOCKS &amp; KEYS (6310)</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="6" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="M105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="6">
+        <f>SUM(C105:N105)</f>
+        <v/>
+      </c>
+      <c r="P105" s="6">
+        <f>SUM(L105:N105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>GROUND SUPPLIES (6510)</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>864.79</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>334.36</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="6" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L106" s="6" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="M106" s="6" t="n">
+        <v>101.73</v>
+      </c>
+      <c r="N106" s="6" t="n">
+        <v>160.49</v>
+      </c>
+      <c r="O106" s="6">
+        <f>SUM(C106:N106)</f>
+        <v/>
+      </c>
+      <c r="P106" s="6">
+        <f>SUM(L106:N106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>POOL SUPPLIES (6520)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>642.01</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>2474.57</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>1025.99</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>270.35</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>515.14</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="6" t="n">
+        <v>768.23</v>
+      </c>
+      <c r="L107" s="6" t="n">
+        <v>232.17</v>
+      </c>
+      <c r="M107" s="6" t="n">
+        <v>822.38</v>
+      </c>
+      <c r="N107" s="6" t="n">
+        <v>690.84</v>
+      </c>
+      <c r="O107" s="6">
+        <f>SUM(C107:N107)</f>
+        <v/>
+      </c>
+      <c r="P107" s="6">
+        <f>SUM(L107:N107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>JANITORIAL SUPPLIES (6540)</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>364.59</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>545.3099999999999</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>517.05</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>176.66</v>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>807.03</v>
+      </c>
+      <c r="L108" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="M108" s="6" t="n">
+        <v>301.42</v>
+      </c>
+      <c r="N108" s="6" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="O108" s="6">
+        <f>SUM(C108:N108)</f>
+        <v/>
+      </c>
+      <c r="P108" s="6">
+        <f>SUM(L108:N108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>GATE/PARKING REPAIRS (6550)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>502.9</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="J109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="6" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="N109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="6">
+        <f>SUM(C109:N109)</f>
+        <v/>
+      </c>
+      <c r="P109" s="6">
+        <f>SUM(L109:N109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>ELECTRICAL SUPPLIES (6560)</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>145.42</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>236.91</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>516.23</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>500.25</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>321.55</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>435.96</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>829.88</v>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>295.94</v>
+      </c>
+      <c r="L110" s="6" t="n">
+        <v>200.07</v>
+      </c>
+      <c r="M110" s="6" t="n">
+        <v>324.49</v>
+      </c>
+      <c r="N110" s="6" t="n">
+        <v>222.22</v>
+      </c>
+      <c r="O110" s="6">
+        <f>SUM(C110:N110)</f>
+        <v/>
+      </c>
+      <c r="P110" s="6">
+        <f>SUM(L110:N110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>PLUMBING SUPPLIES (6570)</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>468.62</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>805.5599999999999</v>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>635.74</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>1011.99</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>1457.51</v>
+      </c>
+      <c r="I111" s="6" t="n">
+        <v>405.05</v>
+      </c>
+      <c r="J111" s="6" t="n">
+        <v>855.23</v>
+      </c>
+      <c r="K111" s="6" t="n">
+        <v>1468.49</v>
+      </c>
+      <c r="L111" s="6" t="n">
+        <v>584.45</v>
+      </c>
+      <c r="M111" s="6" t="n">
+        <v>445.64</v>
+      </c>
+      <c r="N111" s="6" t="n">
+        <v>393.84</v>
+      </c>
+      <c r="O111" s="6">
+        <f>SUM(C111:N111)</f>
+        <v/>
+      </c>
+      <c r="P111" s="6">
+        <f>SUM(L111:N111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>BUILDING REPAIRS (6610)</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>270.27</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>284.67</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>913.01</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>106.88</v>
+      </c>
+      <c r="K112" s="6" t="n">
+        <v>226.67</v>
+      </c>
+      <c r="L112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="6">
+        <f>SUM(C112:N112)</f>
+        <v/>
+      </c>
+      <c r="P112" s="6">
+        <f>SUM(L112:N112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>SCREENS (6640)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="6">
+        <f>SUM(C113:N113)</f>
+        <v/>
+      </c>
+      <c r="P113" s="6">
+        <f>SUM(L113:N113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>GLASS (6660)</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="L114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="6">
+        <f>SUM(C114:N114)</f>
+        <v/>
+      </c>
+      <c r="P114" s="6">
+        <f>SUM(L114:N114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>BLDG. INTERIOR MAINT. (6670)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="6" t="n">
+        <v>11014.3</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>-11014.3</v>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="6">
+        <f>SUM(C115:N115)</f>
+        <v/>
+      </c>
+      <c r="P115" s="6">
+        <f>SUM(L115:N115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>INTERIOR PAINT SUPPLIES - TURN (6700)</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Unit Turns</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>856.37</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>1422.91</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>754.34</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>749.72</v>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>3593.36</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>2019.3</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>213.39</v>
+      </c>
+      <c r="K116" s="6" t="n">
+        <v>1032.59</v>
+      </c>
+      <c r="L116" s="6" t="n">
+        <v>1963.8</v>
+      </c>
+      <c r="M116" s="6" t="n">
+        <v>675.16</v>
+      </c>
+      <c r="N116" s="6" t="n">
+        <v>1122.77</v>
+      </c>
+      <c r="O116" s="6">
+        <f>SUM(C116:N116)</f>
+        <v/>
+      </c>
+      <c r="P116" s="6">
+        <f>SUM(L116:N116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>FILTERS (6720)</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>123.63</v>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>231.33</v>
+      </c>
+      <c r="H117" s="6" t="n">
+        <v>192.73</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="6" t="n">
+        <v>121.58</v>
+      </c>
+      <c r="L117" s="6" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="M117" s="6" t="n">
+        <v>129.33</v>
+      </c>
+      <c r="N117" s="6" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="O117" s="6">
+        <f>SUM(C117:N117)</f>
+        <v/>
+      </c>
+      <c r="P117" s="6">
+        <f>SUM(L117:N117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>HVAC PARTS (6730)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>392.58</v>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>581.72</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>691.02</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>227.19</v>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>406.04</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v>632.46</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>151.06</v>
+      </c>
+      <c r="K118" s="6" t="n">
+        <v>208.11</v>
+      </c>
+      <c r="L118" s="6" t="n">
+        <v>822.8</v>
+      </c>
+      <c r="M118" s="6" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="N118" s="6" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="O118" s="6">
+        <f>SUM(C118:N118)</f>
+        <v/>
+      </c>
+      <c r="P118" s="6">
+        <f>SUM(L118:N118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>APPLIANCE PARTS (6760)</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>400.94</v>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v>111.47</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>199.43</v>
+      </c>
+      <c r="G119" s="6" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="H119" s="6" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>682.17</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>568.61</v>
+      </c>
+      <c r="K119" s="6" t="n">
+        <v>604.64</v>
+      </c>
+      <c r="L119" s="6" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="M119" s="6" t="n">
+        <v>546.8200000000001</v>
+      </c>
+      <c r="N119" s="6" t="n">
+        <v>635.9299999999999</v>
+      </c>
+      <c r="O119" s="6">
+        <f>SUM(C119:N119)</f>
+        <v/>
+      </c>
+      <c r="P119" s="6">
+        <f>SUM(L119:N119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>HARDWARE (6770)</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="6" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="K120" s="6" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="L120" s="6" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="M120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="6">
+        <f>SUM(C120:N120)</f>
+        <v/>
+      </c>
+      <c r="P120" s="6">
+        <f>SUM(L120:N120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>TOOLS &amp; EQUIPMENT (6830)</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="D121" s="6" t="n">
+        <v>138.64</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="6" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="6" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L121" s="6" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="M121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="6" t="n">
+        <v>172.77</v>
+      </c>
+      <c r="O121" s="6">
+        <f>SUM(C121:N121)</f>
+        <v/>
+      </c>
+      <c r="P121" s="6">
+        <f>SUM(L121:N121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>UNIFORMS (6870)</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="6" t="n">
+        <v>170.55</v>
+      </c>
+      <c r="L122" s="6" t="n">
+        <v>311.56</v>
+      </c>
+      <c r="M122" s="6" t="n">
+        <v>190.42</v>
+      </c>
+      <c r="N122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="6">
+        <f>SUM(C122:N122)</f>
+        <v/>
+      </c>
+      <c r="P122" s="6">
+        <f>SUM(L122:N122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>GAS (7010)</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>392.22</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>409.86</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>398.15</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>414.76</v>
+      </c>
+      <c r="H123" s="6" t="n">
+        <v>470.68</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>460.93</v>
+      </c>
+      <c r="K123" s="6" t="n">
+        <v>460.03</v>
+      </c>
+      <c r="L123" s="6" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="M123" s="6" t="n">
+        <v>427.16</v>
+      </c>
+      <c r="N123" s="6" t="n">
+        <v>439.99</v>
+      </c>
+      <c r="O123" s="6">
+        <f>SUM(C123:N123)</f>
+        <v/>
+      </c>
+      <c r="P123" s="6">
+        <f>SUM(L123:N123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>TRASH REMOVAL (7025)</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>4511.02</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>3886.08</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>5024.75</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>4350.78</v>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>4350.78</v>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>4899.3</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>5208.9</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>6250.3</v>
+      </c>
+      <c r="K124" s="6" t="n">
+        <v>4702.9</v>
+      </c>
+      <c r="L124" s="6" t="n">
+        <v>6409</v>
+      </c>
+      <c r="M124" s="6" t="n">
+        <v>4846.6</v>
+      </c>
+      <c r="N124" s="6" t="n">
+        <v>5664.3</v>
+      </c>
+      <c r="O124" s="6">
+        <f>SUM(C124:N124)</f>
+        <v/>
+      </c>
+      <c r="P124" s="6">
+        <f>SUM(L124:N124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>VALET TRASH (7026)</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>3414</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>3414</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>2949.3</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>2949.3</v>
+      </c>
+      <c r="G125" s="6" t="n">
+        <v>2949.3</v>
+      </c>
+      <c r="H125" s="6" t="n">
+        <v>3413.48</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>3507</v>
+      </c>
+      <c r="J125" s="6" t="n">
+        <v>3519.3</v>
+      </c>
+      <c r="K125" s="6" t="n">
+        <v>3519.3</v>
+      </c>
+      <c r="L125" s="6" t="n">
+        <v>3729.3</v>
+      </c>
+      <c r="M125" s="6" t="n">
+        <v>3389.7</v>
+      </c>
+      <c r="N125" s="6" t="n">
+        <v>2391.6</v>
+      </c>
+      <c r="O125" s="6">
+        <f>SUM(C125:N125)</f>
+        <v/>
+      </c>
+      <c r="P125" s="6">
+        <f>SUM(L125:N125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>ELECTRICITY - COMMON AREA (7030)</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>2782.73</v>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>2892.56</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>2409.63</v>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>2022.4</v>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>1549.24</v>
+      </c>
+      <c r="H126" s="6" t="n">
+        <v>1503.68</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v>1568.53</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>1454.66</v>
+      </c>
+      <c r="K126" s="6" t="n">
+        <v>1515.05</v>
+      </c>
+      <c r="L126" s="6" t="n">
+        <v>1758.84</v>
+      </c>
+      <c r="M126" s="6" t="n">
+        <v>1937.45</v>
+      </c>
+      <c r="N126" s="6" t="n">
+        <v>2111.83</v>
+      </c>
+      <c r="O126" s="6">
+        <f>SUM(C126:N126)</f>
+        <v/>
+      </c>
+      <c r="P126" s="6">
+        <f>SUM(L126:N126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>ELECTRICITY - VACANT (7040)</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>2753.82</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>1969.09</v>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>2234.67</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>295.03</v>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>1725.2</v>
+      </c>
+      <c r="H127" s="6" t="n">
+        <v>942.34</v>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>954.05</v>
+      </c>
+      <c r="J127" s="6" t="n">
+        <v>829.15</v>
+      </c>
+      <c r="K127" s="6" t="n">
+        <v>541.16</v>
+      </c>
+      <c r="L127" s="6" t="n">
+        <v>789</v>
+      </c>
+      <c r="M127" s="6" t="n">
+        <v>1195.52</v>
+      </c>
+      <c r="N127" s="6" t="n">
+        <v>1143.73</v>
+      </c>
+      <c r="O127" s="6">
+        <f>SUM(C127:N127)</f>
+        <v/>
+      </c>
+      <c r="P127" s="6">
+        <f>SUM(L127:N127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>RECOVERABLE ELEC/GAS/WATER (7050)</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>682.3200000000001</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>247.69</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>955.85</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="G128" s="6" t="n">
+        <v>448.56</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>512.4400000000001</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>254.24</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="K128" s="6" t="n">
+        <v>207.67</v>
+      </c>
+      <c r="L128" s="6" t="n">
+        <v>-22.16</v>
+      </c>
+      <c r="M128" s="6" t="n">
+        <v>248.96</v>
+      </c>
+      <c r="N128" s="6" t="n">
+        <v>271.98</v>
+      </c>
+      <c r="O128" s="6">
+        <f>SUM(C128:N128)</f>
+        <v/>
+      </c>
+      <c r="P128" s="6">
+        <f>SUM(L128:N128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>WATER (7060)</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>9466.18</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>10612.86</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>9434.09</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>9072.84</v>
+      </c>
+      <c r="G129" s="6" t="n">
+        <v>7106.59</v>
+      </c>
+      <c r="H129" s="6" t="n">
+        <v>9086.219999999999</v>
+      </c>
+      <c r="I129" s="6" t="n">
+        <v>8551.09</v>
+      </c>
+      <c r="J129" s="6" t="n">
+        <v>8447.51</v>
+      </c>
+      <c r="K129" s="6" t="n">
+        <v>8273.49</v>
+      </c>
+      <c r="L129" s="6" t="n">
+        <v>8756.049999999999</v>
+      </c>
+      <c r="M129" s="6" t="n">
+        <v>8957.620000000001</v>
+      </c>
+      <c r="N129" s="6" t="n">
+        <v>9916.76</v>
+      </c>
+      <c r="O129" s="6">
+        <f>SUM(C129:N129)</f>
+        <v/>
+      </c>
+      <c r="P129" s="6">
+        <f>SUM(L129:N129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>SEWAGE (7070)</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>7815.28</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>8744.389999999999</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>7789.25</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>7496.6</v>
+      </c>
+      <c r="G130" s="6" t="n">
+        <v>5903.49</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>7507.42</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>6990.32</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>6907.55</v>
+      </c>
+      <c r="K130" s="6" t="n">
+        <v>6768.51</v>
+      </c>
+      <c r="L130" s="6" t="n">
+        <v>7154.11</v>
+      </c>
+      <c r="M130" s="6" t="n">
+        <v>7315.2</v>
+      </c>
+      <c r="N130" s="6" t="n">
+        <v>8081.7</v>
+      </c>
+      <c r="O130" s="6">
+        <f>SUM(C130:N130)</f>
+        <v/>
+      </c>
+      <c r="P130" s="6">
+        <f>SUM(L130:N130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>UTILITY BILLING EXPENSE (7075)</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>954</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>955.15</v>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v>915.65</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>912.7</v>
+      </c>
+      <c r="G131" s="6" t="n">
+        <v>926.3</v>
+      </c>
+      <c r="H131" s="6" t="n">
+        <v>896.8</v>
+      </c>
+      <c r="I131" s="6" t="n">
+        <v>905.65</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>929.25</v>
+      </c>
+      <c r="K131" s="6" t="n">
+        <v>960.15</v>
+      </c>
+      <c r="L131" s="6" t="n">
+        <v>953.35</v>
+      </c>
+      <c r="M131" s="6" t="n">
+        <v>931.55</v>
+      </c>
+      <c r="N131" s="6" t="n">
+        <v>967.85</v>
+      </c>
+      <c r="O131" s="6">
+        <f>SUM(C131:N131)</f>
+        <v/>
+      </c>
+      <c r="P131" s="6">
+        <f>SUM(L131:N131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>REAL ESTATE TAXES (7110)</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>20372</v>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>20372</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>20372</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>24253.32</v>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v>20760.13</v>
+      </c>
+      <c r="H132" s="6" t="n">
+        <v>20760.13</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="K132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="L132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="M132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="N132" s="6" t="n">
+        <v>20881</v>
+      </c>
+      <c r="O132" s="6">
+        <f>SUM(C132:N132)</f>
+        <v/>
+      </c>
+      <c r="P132" s="6">
+        <f>SUM(L132:N132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>LICENSES &amp; FEES (7130)</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="6" t="n">
+        <v>1574.06</v>
+      </c>
+      <c r="M133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="6">
+        <f>SUM(C133:N133)</f>
+        <v/>
+      </c>
+      <c r="P133" s="6">
+        <f>SUM(L133:N133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>LIABILITY INSURANCE (7210)</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>6331.19</v>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>6331.19</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>6331.19</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="G134" s="6" t="n">
+        <v>7202.44</v>
+      </c>
+      <c r="H134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="K134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="L134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="M134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="N134" s="6" t="n">
+        <v>6121.52</v>
+      </c>
+      <c r="O134" s="6">
+        <f>SUM(C134:N134)</f>
+        <v/>
+      </c>
+      <c r="P134" s="6">
+        <f>SUM(L134:N134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>PROPERTY INSURANCE (7220)</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="D135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="G135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="H135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="I135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="J135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="K135" s="6" t="n">
+        <v>8505.389999999999</v>
+      </c>
+      <c r="L135" s="6" t="n">
+        <v>8505.43</v>
+      </c>
+      <c r="M135" s="6" t="n">
+        <v>7229.58</v>
+      </c>
+      <c r="N135" s="6" t="n">
+        <v>6390.42</v>
+      </c>
+      <c r="O135" s="6">
+        <f>SUM(C135:N135)</f>
+        <v/>
+      </c>
+      <c r="P135" s="6">
+        <f>SUM(L135:N135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Monthly revenue (computed)</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="C39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
-        <v/>
-      </c>
-      <c r="F39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
-        <v/>
-      </c>
-      <c r="H39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
-        <v/>
-      </c>
-      <c r="I39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
-        <v/>
-      </c>
-      <c r="J39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
-        <v/>
-      </c>
-      <c r="K39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
-        <v/>
-      </c>
-      <c r="L39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
-        <v/>
-      </c>
-      <c r="M39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
-        <v/>
-      </c>
-      <c r="N39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
-        <v/>
-      </c>
-      <c r="O39" s="11">
-        <f>SUM(C39:N39)</f>
-        <v/>
-      </c>
-      <c r="P39" s="11">
-        <f>SUM(L39:N39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="C137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",C$6:C$135),SUMIF($B$6:$B$135,"Gross Potential Rent",C$6:C$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",C$6:C$135))+SUMIF($B$6:$B$135,"Vacancy",C$6:C$135)+SUMIF($B$6:$B$135,"Concessions",C$6:C$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",C$6:C$135)+SUMIF($B$6:$B$135,"Delinquency",C$6:C$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",C$6:C$135)+SUMIF($B$6:$B$135,"Other Income",C$6:C$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",C$6:C$135)</f>
+        <v/>
+      </c>
+      <c r="D137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",D$6:D$135),SUMIF($B$6:$B$135,"Gross Potential Rent",D$6:D$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",D$6:D$135))+SUMIF($B$6:$B$135,"Vacancy",D$6:D$135)+SUMIF($B$6:$B$135,"Concessions",D$6:D$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",D$6:D$135)+SUMIF($B$6:$B$135,"Delinquency",D$6:D$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",D$6:D$135)+SUMIF($B$6:$B$135,"Other Income",D$6:D$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",D$6:D$135)</f>
+        <v/>
+      </c>
+      <c r="E137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",E$6:E$135),SUMIF($B$6:$B$135,"Gross Potential Rent",E$6:E$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",E$6:E$135))+SUMIF($B$6:$B$135,"Vacancy",E$6:E$135)+SUMIF($B$6:$B$135,"Concessions",E$6:E$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",E$6:E$135)+SUMIF($B$6:$B$135,"Delinquency",E$6:E$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",E$6:E$135)+SUMIF($B$6:$B$135,"Other Income",E$6:E$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",E$6:E$135)</f>
+        <v/>
+      </c>
+      <c r="F137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",F$6:F$135),SUMIF($B$6:$B$135,"Gross Potential Rent",F$6:F$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",F$6:F$135))+SUMIF($B$6:$B$135,"Vacancy",F$6:F$135)+SUMIF($B$6:$B$135,"Concessions",F$6:F$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",F$6:F$135)+SUMIF($B$6:$B$135,"Delinquency",F$6:F$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",F$6:F$135)+SUMIF($B$6:$B$135,"Other Income",F$6:F$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",F$6:F$135)</f>
+        <v/>
+      </c>
+      <c r="G137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",G$6:G$135),SUMIF($B$6:$B$135,"Gross Potential Rent",G$6:G$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",G$6:G$135))+SUMIF($B$6:$B$135,"Vacancy",G$6:G$135)+SUMIF($B$6:$B$135,"Concessions",G$6:G$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",G$6:G$135)+SUMIF($B$6:$B$135,"Delinquency",G$6:G$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",G$6:G$135)+SUMIF($B$6:$B$135,"Other Income",G$6:G$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",G$6:G$135)</f>
+        <v/>
+      </c>
+      <c r="H137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",H$6:H$135),SUMIF($B$6:$B$135,"Gross Potential Rent",H$6:H$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",H$6:H$135))+SUMIF($B$6:$B$135,"Vacancy",H$6:H$135)+SUMIF($B$6:$B$135,"Concessions",H$6:H$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",H$6:H$135)+SUMIF($B$6:$B$135,"Delinquency",H$6:H$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",H$6:H$135)+SUMIF($B$6:$B$135,"Other Income",H$6:H$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",H$6:H$135)</f>
+        <v/>
+      </c>
+      <c r="I137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",I$6:I$135),SUMIF($B$6:$B$135,"Gross Potential Rent",I$6:I$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",I$6:I$135))+SUMIF($B$6:$B$135,"Vacancy",I$6:I$135)+SUMIF($B$6:$B$135,"Concessions",I$6:I$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",I$6:I$135)+SUMIF($B$6:$B$135,"Delinquency",I$6:I$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",I$6:I$135)+SUMIF($B$6:$B$135,"Other Income",I$6:I$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",I$6:I$135)</f>
+        <v/>
+      </c>
+      <c r="J137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",J$6:J$135),SUMIF($B$6:$B$135,"Gross Potential Rent",J$6:J$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",J$6:J$135))+SUMIF($B$6:$B$135,"Vacancy",J$6:J$135)+SUMIF($B$6:$B$135,"Concessions",J$6:J$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",J$6:J$135)+SUMIF($B$6:$B$135,"Delinquency",J$6:J$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",J$6:J$135)+SUMIF($B$6:$B$135,"Other Income",J$6:J$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",J$6:J$135)</f>
+        <v/>
+      </c>
+      <c r="K137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",K$6:K$135),SUMIF($B$6:$B$135,"Gross Potential Rent",K$6:K$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",K$6:K$135))+SUMIF($B$6:$B$135,"Vacancy",K$6:K$135)+SUMIF($B$6:$B$135,"Concessions",K$6:K$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",K$6:K$135)+SUMIF($B$6:$B$135,"Delinquency",K$6:K$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",K$6:K$135)+SUMIF($B$6:$B$135,"Other Income",K$6:K$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",K$6:K$135)</f>
+        <v/>
+      </c>
+      <c r="L137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",L$6:L$135),SUMIF($B$6:$B$135,"Gross Potential Rent",L$6:L$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",L$6:L$135))+SUMIF($B$6:$B$135,"Vacancy",L$6:L$135)+SUMIF($B$6:$B$135,"Concessions",L$6:L$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",L$6:L$135)+SUMIF($B$6:$B$135,"Delinquency",L$6:L$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",L$6:L$135)+SUMIF($B$6:$B$135,"Other Income",L$6:L$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",L$6:L$135)</f>
+        <v/>
+      </c>
+      <c r="M137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",M$6:M$135),SUMIF($B$6:$B$135,"Gross Potential Rent",M$6:M$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",M$6:M$135))+SUMIF($B$6:$B$135,"Vacancy",M$6:M$135)+SUMIF($B$6:$B$135,"Concessions",M$6:M$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",M$6:M$135)+SUMIF($B$6:$B$135,"Delinquency",M$6:M$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",M$6:M$135)+SUMIF($B$6:$B$135,"Other Income",M$6:M$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",M$6:M$135)</f>
+        <v/>
+      </c>
+      <c r="N137" s="8">
+        <f>IF(COUNTIF($B$6:$B$135,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$135,"Gross Scheduled Rent",N$6:N$135),SUMIF($B$6:$B$135,"Gross Potential Rent",N$6:N$135)+SUMIF($B$6:$B$135,"Gain/(Loss) to Lease",N$6:N$135))+SUMIF($B$6:$B$135,"Vacancy",N$6:N$135)+SUMIF($B$6:$B$135,"Concessions",N$6:N$135)+SUMIF($B$6:$B$135,"Non-Revenue Units",N$6:N$135)+SUMIF($B$6:$B$135,"Delinquency",N$6:N$135)+SUMIF($B$6:$B$135,"Utility Reimbursements",N$6:N$135)+SUMIF($B$6:$B$135,"Other Income",N$6:N$135)+SUMIF($B$6:$B$135,"Revenue Adjustments",N$6:N$135)</f>
+        <v/>
+      </c>
+      <c r="O137" s="8">
+        <f>SUM(C137:N137)</f>
+        <v/>
+      </c>
+      <c r="P137" s="8">
+        <f>SUM(L137:N137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Revenue by month, built from the same category SUMIFs as the rollup. Gross scheduled rent falls back to gross potential rent plus gain/(loss) to lease where the statement did not print it.</t>
         </is>
@@ -2510,7 +8002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2530,7 +8022,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fixture Park — as of 2026-06-30</t>
+          <t>505 West — as of 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -2579,576 +8071,576 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Gross Potential Rent</t>
         </is>
       </c>
-      <c r="B6" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A6,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C6" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A6,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>IFERROR(B6/180,"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
+      <c r="B6" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C6" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>IFERROR(B6/334,"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
         <f>IFERROR(B6/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Gain/(Loss) to Lease</t>
         </is>
       </c>
-      <c r="B7" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A7,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A7,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>IFERROR(B7/180,"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="14">
+      <c r="B7" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C7" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D7" s="10">
+        <f>IFERROR(B7/334,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
         <f>IFERROR(B7/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Gross Scheduled Rent</t>
         </is>
       </c>
-      <c r="B8" s="9">
-        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$37,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$O$6:$O$37),B6+B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
-        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$37,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$37,$A8,'T-12 Data'!$P$6:$P$37)*4,(C6+C7))</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>IFERROR(B8/180,"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
+      <c r="B8" s="13">
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$O$6:$O$135),B6+B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="13">
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$P$6:$P$135)*4,(C6+C7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>IFERROR(B8/334,"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="14">
         <f>IFERROR(B8/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="B9" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A9,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A9,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>IFERROR(B9/180,"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
+      <c r="B9" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C9" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f>IFERROR(B9/334,"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
         <f>IFERROR(B9/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Concessions</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A10,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A10,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>IFERROR(B10/180,"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="14">
+      <c r="B10" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C10" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D10" s="10">
+        <f>IFERROR(B10/334,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
         <f>IFERROR(B10/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Non-Revenue Units</t>
         </is>
       </c>
-      <c r="B11" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A11,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C11" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A11,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D11" s="13">
-        <f>IFERROR(B11/180,"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
+      <c r="B11" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C11" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f>IFERROR(B11/334,"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
         <f>IFERROR(B11/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Delinquency</t>
         </is>
       </c>
-      <c r="B12" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A12,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C12" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A12,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D12" s="13">
-        <f>IFERROR(B12/180,"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="14">
+      <c r="B12" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>IFERROR(B12/334,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
         <f>IFERROR(B12/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Utility Reimbursements</t>
         </is>
       </c>
-      <c r="B13" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A13,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C13" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A13,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D13" s="13">
-        <f>IFERROR(B13/180,"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
+      <c r="B13" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D13" s="10">
+        <f>IFERROR(B13/334,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
         <f>IFERROR(B13/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B14" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A14,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C14" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A14,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D14" s="13">
-        <f>IFERROR(B14/180,"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
+      <c r="B14" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D14" s="10">
+        <f>IFERROR(B14/334,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
         <f>IFERROR(B14/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Revenue Adjustments</t>
         </is>
       </c>
-      <c r="B15" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A15,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C15" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A15,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D15" s="13">
-        <f>IFERROR(B15/180,"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
+      <c r="B15" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C15" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f>IFERROR(B15/334,"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
         <f>IFERROR(B15/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="13">
         <f>SUM(B8:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="13">
         <f>SUM(C8:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="9">
-        <f>IFERROR(B16/180,"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16" s="13">
+        <f>IFERROR(B16/334,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
         <f>IFERROR(B16/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A17,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C17" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A17,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>IFERROR(B17/180,"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
+      <c r="B17" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C17" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D17" s="10">
+        <f>IFERROR(B17/334,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
         <f>IFERROR(B17/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Leasing and Marketing</t>
         </is>
       </c>
-      <c r="B18" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A18,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C18" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A18,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D18" s="13">
-        <f>IFERROR(B18/180,"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="14">
+      <c r="B18" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C18" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D18" s="10">
+        <f>IFERROR(B18/334,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
         <f>IFERROR(B18/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B19" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A19,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C19" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A19,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D19" s="13">
-        <f>IFERROR(B19/180,"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="14">
+      <c r="B19" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C19" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>IFERROR(B19/334,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
         <f>IFERROR(B19/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B20" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A20,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C20" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A20,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>IFERROR(B20/180,"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="14">
+      <c r="B20" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C20" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D20" s="10">
+        <f>IFERROR(B20/334,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
         <f>IFERROR(B20/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Property Taxes</t>
         </is>
       </c>
-      <c r="B21" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A21,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C21" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A21,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D21" s="13">
-        <f>IFERROR(B21/180,"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="14">
+      <c r="B21" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C21" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D21" s="10">
+        <f>IFERROR(B21/334,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
         <f>IFERROR(B21/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Legal and Professional</t>
         </is>
       </c>
-      <c r="B22" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A22,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C22" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A22,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D22" s="13">
-        <f>IFERROR(B22/180,"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="14">
+      <c r="B22" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C22" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D22" s="10">
+        <f>IFERROR(B22/334,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
         <f>IFERROR(B22/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Management Fee</t>
         </is>
       </c>
-      <c r="B23" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A23,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C23" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A23,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D23" s="13">
-        <f>IFERROR(B23/180,"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="14">
+      <c r="B23" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C23" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D23" s="10">
+        <f>IFERROR(B23/334,"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
         <f>IFERROR(B23/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Landscaping</t>
         </is>
       </c>
-      <c r="B24" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A24,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C24" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A24,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D24" s="13">
-        <f>IFERROR(B24/180,"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="14">
+      <c r="B24" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C24" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D24" s="10">
+        <f>IFERROR(B24/334,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
         <f>IFERROR(B24/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Repairs and Maintenance</t>
         </is>
       </c>
-      <c r="B25" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A25,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C25" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A25,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D25" s="13">
-        <f>IFERROR(B25/180,"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
+      <c r="B25" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C25" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D25" s="10">
+        <f>IFERROR(B25/334,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
         <f>IFERROR(B25/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Unit Turns</t>
         </is>
       </c>
-      <c r="B26" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A26,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C26" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A26,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D26" s="13">
-        <f>IFERROR(B26/180,"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
+      <c r="B26" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C26" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>IFERROR(B26/334,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
         <f>IFERROR(B26/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B27" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A27,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A27,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>IFERROR(B27/180,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
+      <c r="B27" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C27" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D27" s="10">
+        <f>IFERROR(B27/334,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
         <f>IFERROR(B27/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Expense Adjustments</t>
         </is>
       </c>
-      <c r="B28" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A28,'T-12 Data'!$O$6:$O$37)</f>
-        <v/>
-      </c>
-      <c r="C28" s="13">
-        <f>SUMIF('T-12 Data'!$B$6:$B$37,$A28,'T-12 Data'!$P$6:$P$37)*4</f>
-        <v/>
-      </c>
-      <c r="D28" s="13">
-        <f>IFERROR(B28/180,"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="14">
+      <c r="B28" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$O$6:$O$135)</f>
+        <v/>
+      </c>
+      <c r="C28" s="10">
+        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$P$6:$P$135)*4</f>
+        <v/>
+      </c>
+      <c r="D28" s="10">
+        <f>IFERROR(B28/334,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="11">
         <f>IFERROR(B28/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Total Operating Expenses</t>
         </is>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="13">
         <f>SUM(B17:B28)</f>
         <v/>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="13">
         <f>SUM(C17:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="9">
-        <f>IFERROR(B29/180,"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="15">
+      <c r="D29" s="13">
+        <f>IFERROR(B29/334,"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
         <f>IFERROR(B29/B16,"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="13">
         <f>B16-B29</f>
         <v/>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="13">
         <f>C16-C29</f>
         <v/>
       </c>
-      <c r="D30" s="9">
-        <f>IFERROR(B30/180,"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30" s="13">
+        <f>IFERROR(B30/334,"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="14">
         <f>IFERROR(B30/B16,"")</f>
         <v/>
       </c>
@@ -3161,13 +8653,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Other Income — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3189,91 +8681,91 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Pet Rent</t>
+          <t>TERMINATION FEE (3112)</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>47600.04</v>
+        <v>104626.65</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>48449.88</v>
+        <v>81552</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>TENANT DAMAGE REIMBURSEMENT (3040)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>37851.11</v>
+        <v>58881.05</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>38529.88</v>
+        <v>38744</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Late Fees</t>
+          <t>RENTER'S INSURANCE INCOME (3175)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>17686.93</v>
+        <v>57363.31</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>18098.92</v>
+        <v>59842.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Application Fees</t>
+          <t>RENTER'S INSURANCE EXPENSE (3176)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>14384.28</v>
+        <v>-50810.29</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>14702.76</v>
+        <v>-51916.56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>All other other income (2 lines)</t>
+          <t>All other other income (18 lines)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>14382.27</v>
+        <v>230301.76</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>14702.72</v>
+        <v>212762.56</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Total other income</t>
         </is>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="13">
         <f>'P&amp;L Summary'!B14</f>
         <v/>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="13">
         <f>'P&amp;L Summary'!C14</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Utility Reimbursements — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3295,159 +8787,185 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>RUBS — Water/Sewer</t>
+          <t>WATER/SEWER REIMBURSEMENT (3186)</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>119632.39</v>
+        <v>190868.88</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>121915.56</v>
+        <v>183652.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RUBS — Trash</t>
+          <t>VALET TRASH REIMBURSEMENTS (3001)</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>51631.87</v>
+        <v>83725.62</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>52751.8</v>
+        <v>93002.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>All other utility reimbursements (0 lines)</t>
+          <t>TRASH REIMBURSEMENT (3187)</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0</v>
+        <v>44528.14</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0</v>
+        <v>37222.36</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Total utility reimbursements</t>
-        </is>
-      </c>
-      <c r="B48" s="9">
-        <f>'P&amp;L Summary'!B13</f>
-        <v/>
-      </c>
-      <c r="C48" s="9">
-        <f>'P&amp;L Summary'!C13</f>
-        <v/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>UTILITY FEE REIMBURSEMENT (3183)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>13255.7</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>13120.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>All other utility reimbursements (2 lines)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>5569.1</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>3453.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
+          <t>Total utility reimbursements</t>
+        </is>
+      </c>
+      <c r="B50" s="13">
+        <f>'P&amp;L Summary'!B13</f>
+        <v/>
+      </c>
+      <c r="C50" s="13">
+        <f>'P&amp;L Summary'!C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
           <t>Utilities — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>T-3 annualized</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Utilities — Water/Sewer</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>114812.93</v>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>117279.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Utilities — Electric (common)</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>51338.87</v>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>51863.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Trash</t>
+          <t>WATER (7060)</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>50156.25</v>
+        <v>107681.3</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>51141.8</v>
+        <v>110521.72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Utilities — Gas</t>
+          <t>SEWAGE (7070)</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>28111.16</v>
+        <v>88473.81999999999</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>28709.92</v>
+        <v>90204.03999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>All other utilities (1 lines)</t>
+          <t>TRASH REMOVAL (7025)</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>19532.84</v>
+        <v>60104.71</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>19983.92</v>
+        <v>67679.60000000001</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>VALET TRASH (7026)</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>39145.58</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>38042.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>All other utilities (5 lines)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>59505.22</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>54354</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Total utilities</t>
         </is>
       </c>
-      <c r="B57" s="9">
+      <c r="B59" s="13">
         <f>'P&amp;L Summary'!B27</f>
         <v/>
       </c>
-      <c r="C57" s="9">
+      <c r="C59" s="13">
         <f>'P&amp;L Summary'!C27</f>
         <v/>
       </c>
@@ -3463,7 +8981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3484,7 +9002,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fixture Park — as of 2026-06-30</t>
+          <t>505 West — as of 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -3506,16 +9024,16 @@
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Error check</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3560,7 +9078,7 @@
         <v/>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3814903.84</v>
+        <v>5606053.56</v>
       </c>
       <c r="D7" s="6">
         <f>IFERROR(B7-C7,"")</f>
@@ -3583,7 +9101,7 @@
         <v/>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1688442.2</v>
+        <v>2163060.96</v>
       </c>
       <c r="D8" s="6">
         <f>IFERROR(B8-C8,"")</f>
@@ -3606,7 +9124,7 @@
         <v/>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2126461.64</v>
+        <v>3442992.6</v>
       </c>
       <c r="D9" s="6">
         <f>IFERROR(B9-C9,"")</f>
@@ -3628,9 +9146,7 @@
         <f>'P&amp;L Summary'!B14</f>
         <v/>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>131904.63</v>
-      </c>
+      <c r="C10" s="17" t="n"/>
       <c r="D10" s="6">
         <f>IFERROR(B10-C10,"")</f>
         <v/>
@@ -3639,7 +9155,11 @@
         <f>IF(C10="","NOT CHECKED",IF(ABS(D10)&lt;=1,"OK","REVIEW"))</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>The source statement printed no subtotal for this line.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3677,7 +9197,7 @@
         <v/>
       </c>
       <c r="C12" s="6" t="n">
-        <v>263952.05</v>
+        <v>354910.63</v>
       </c>
       <c r="D12" s="6">
         <f>IFERROR(B12-C12,"")</f>
@@ -3697,16 +9217,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Pricing and cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3715,11 +9235,11 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>215000</v>
+        <v>180000</v>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative pricing. $180,000 per unit is a round figure chosen inside the band a real per-unit sale price occupies, set so the resulting cap rate sits within 150 basis points of the level the trailing-twelve income supports. The guidance this deal was actually marketed at is not reproduced anywhere in this output set.</t>
         </is>
       </c>
     </row>
@@ -3730,7 +9250,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>180</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19">
@@ -3833,112 +9353,66 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Broker pro forma revenue</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>4051427.88</v>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Kept in its own block; never merged into the T-12.</t>
-        </is>
-      </c>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Revenue trend</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma operating expenses</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>1718834.16</v>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma net operating income</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>2332593.72</v>
+          <t>T-6 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>SUM('T-12 Data'!I137:N137)*2</f>
+        <v/>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B34" s="19">
-        <f>IFERROR(B33/B19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Revenue trend</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B37" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>T-6 revenue (annualized)</t>
-        </is>
-      </c>
-      <c r="B38" s="6">
-        <f>SUM('T-12 Data'!I39:N39)*2</f>
-        <v/>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
           <t>T-3 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B39" s="6">
+      <c r="B34" s="6">
         <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B40" s="20">
-        <f>IFERROR(B39/B21-1,"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="B35" s="20">
+        <f>IFERROR(B34/B21-1,"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -10,6 +10,7 @@
     <sheet name="T-12 Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="P&amp;L Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Checks &amp; Pricing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Audit Trail" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,6 +142,13 @@
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3947,4 +3959,251 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Audit trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fixture Park — as of 2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>T-12 data, the P&amp;L rollup and pricing. Every value below names the document it came from and where in it. A derived value names the values it was built from — one that could not would not have passed validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Stamped values in this workbook</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Coverage of the required set</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>42/42 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Source document</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Where in it</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Built from</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Supporting quote / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>pricing.price_per_unit</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>pricing.unit_count</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll!A:A</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>t12.month_labels</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>T-12!C8:N8</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>t12.source_subtotals</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>T-12!O</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>t12.units</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -3971,11 +3971,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4027,7 +4028,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>42/42 (100%)</t>
+          <t>50/50 (100%)</t>
         </is>
       </c>
     </row>
@@ -4039,25 +4040,30 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>Value as published</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>Source document</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Where in it</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>How</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Built from</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Supporting quote / note</t>
         </is>
@@ -4071,21 +4077,26 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>215,000</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
         </is>
@@ -4099,25 +4110,30 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Rent Roll!A:A</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>summary.unit_count</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
@@ -4127,21 +4143,26 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>12 entries</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
           <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>T-12!C8:N8</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
         </is>
@@ -4155,21 +4176,26 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>5 keys</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
           <t>Synthetic trailing-twelve income statement</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>T-12!O</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>The statement's own printed subtotals, kept for the cross-tie.</t>
         </is>
@@ -4183,25 +4209,30 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
           <t>Synthetic rent roll export</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>summary.unit_count</t>
         </is>
       </c>
-      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50/50 (100%)</t>
+          <t>52/52 (100%)</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -137,15 +137,15 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3475,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3711,7 +3711,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Pricing and cap rate (illustrative)</t>
+          <t>Rent-roll tie-outs</t>
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
@@ -3721,236 +3721,728 @@
       <c r="F16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Price per unit</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Our calc</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Unit count</t>
+          <t>Total units</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
         <v>180</v>
       </c>
+      <c r="C18" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Unit count after de-duplicating rows for units listed twice mid-turnover.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Total purchase price</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>B17*B18</f>
-        <v/>
+          <t>Total square feet</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>190440</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>178020</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>12420</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>This project's own addition — the operator's rent-roll skill has no square-footage tie-out. It earns its place because square footage is what the de-duplication is checked against: dropping the wrong duplicate row changes the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0.9833333333333333</v>
+      </c>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>PHYSICAL occupancy: 177 of 180 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>T-12 operating expenses</t>
-        </is>
-      </c>
-      <c r="B22" s="6">
-        <f>'P&amp;L Summary'!B29</f>
-        <v/>
+          <t>Occupied units</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>The numerator above, stated separately so the ratio can be re-derived.</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>T-12 net operating income</t>
-        </is>
-      </c>
-      <c r="B23" s="6">
-        <f>'P&amp;L Summary'!B30</f>
-        <v/>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>1/3 tie-outs OK; 1 NOT CHECKED</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>T-12 cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B24" s="19">
-        <f>IFERROR(B23/B19,"")</f>
-        <v/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 177/180 units, physical. Down, model and employee units count as vacant.</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>T-3 annualized revenue</t>
-        </is>
-      </c>
-      <c r="B26" s="6">
-        <f>'P&amp;L Summary'!C16</f>
-        <v/>
-      </c>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Rent readback — 10 units, sampled reproducibly</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>T-3 annualized operating expenses</t>
-        </is>
-      </c>
-      <c r="B27" s="6">
-        <f>'P&amp;L Summary'!C29</f>
-        <v/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Our in-place rent</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Source cell value</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Source locator</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized net operating income</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <f>'P&amp;L Summary'!C30</f>
-        <v/>
+          <t>A1-123</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1417</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F26</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B29" s="19">
-        <f>IFERROR(B28/B19,"")</f>
-        <v/>
+          <t>A1-130</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1438</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1438</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F33</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>A2-108</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1564</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1564</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F45</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma revenue</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>4051427.88</v>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Kept in its own block; never merged into the T-12.</t>
+          <t>B1-101</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F66</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma operating expenses</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>1718834.16</v>
+          <t>B1-103</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F68</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma net operating income</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>2332593.72</v>
+          <t>B1-113</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1734</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1734</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F78</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B34" s="19">
-        <f>IFERROR(B33/B19,"")</f>
-        <v/>
+          <t>B1-126</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F91</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>B2-123</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F130</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Revenue trend</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>C1-118</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F161</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>Cypress-106</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Cypress TH</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2343</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F175</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-06-30|180), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Pricing and cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Price per unit</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Total purchase price</t>
+        </is>
+      </c>
+      <c r="B45" s="6">
+        <f>B43*B44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>T-12 revenue</t>
         </is>
       </c>
-      <c r="B37" s="6">
+      <c r="B47" s="6">
         <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-12 operating expenses</t>
+        </is>
+      </c>
+      <c r="B48" s="6">
+        <f>'P&amp;L Summary'!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-12 net operating income</t>
+        </is>
+      </c>
+      <c r="B49" s="6">
+        <f>'P&amp;L Summary'!B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>T-12 cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B50" s="21">
+        <f>IFERROR(B49/B45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized operating expenses</t>
+        </is>
+      </c>
+      <c r="B53" s="6">
+        <f>'P&amp;L Summary'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized net operating income</t>
+        </is>
+      </c>
+      <c r="B54" s="6">
+        <f>'P&amp;L Summary'!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B55" s="21">
+        <f>IFERROR(B54/B45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Broker pro forma revenue</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>4051427.88</v>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>Kept in its own block; never merged into the T-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Broker pro forma operating expenses</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>1718834.16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Broker pro forma net operating income</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>2332593.72</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Broker pro forma cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B60" s="21">
+        <f>IFERROR(B59/B45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Revenue trend</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="n"/>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B63" s="6">
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>T-6 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B38" s="6">
+      <c r="B64" s="6">
         <f>SUM('T-12 Data'!I39:N39)*2</f>
         <v/>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr">
         <is>
           <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>T-3 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B39" s="6">
+      <c r="B65" s="6">
         <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B40" s="20">
-        <f>IFERROR(B39/B21-1,"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="B66" s="19">
+        <f>IFERROR(B65/B47-1,"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>
@@ -4070,7 +4562,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>pricing.price_per_unit</t>
         </is>
@@ -4096,14 +4588,14 @@
         </is>
       </c>
       <c r="F9" s="17" t="n"/>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>pricing.unit_count</t>
         </is>
@@ -4136,7 +4628,7 @@
       <c r="G10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>t12.month_labels</t>
         </is>
@@ -4162,14 +4654,14 @@
         </is>
       </c>
       <c r="F11" s="17" t="n"/>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>t12.source_subtotals</t>
         </is>
@@ -4195,14 +4687,14 @@
         </is>
       </c>
       <c r="F12" s="17" t="n"/>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>The statement's own printed subtotals, kept for the cross-tie.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>t12.units</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease</t>
+          <t>Gain / (Loss) to Lease</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
@@ -2448,51 +2448,51 @@
         </is>
       </c>
       <c r="C39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",C$6:C$37),SUMIF($B$6:$B$37,"Gross Potential Rent",C$6:C$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",C$6:C$37))+SUMIF($B$6:$B$37,"Vacancy",C$6:C$37)+SUMIF($B$6:$B$37,"Concessions",C$6:C$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",C$6:C$37)+SUMIF($B$6:$B$37,"Delinquency",C$6:C$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",C$6:C$37)+SUMIF($B$6:$B$37,"Other Income",C$6:C$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",C$6:C$37)</f>
         <v/>
       </c>
       <c r="D39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",D$6:D$37),SUMIF($B$6:$B$37,"Gross Potential Rent",D$6:D$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",D$6:D$37))+SUMIF($B$6:$B$37,"Vacancy",D$6:D$37)+SUMIF($B$6:$B$37,"Concessions",D$6:D$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",D$6:D$37)+SUMIF($B$6:$B$37,"Delinquency",D$6:D$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",D$6:D$37)+SUMIF($B$6:$B$37,"Other Income",D$6:D$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",D$6:D$37)</f>
         <v/>
       </c>
       <c r="E39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",E$6:E$37),SUMIF($B$6:$B$37,"Gross Potential Rent",E$6:E$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",E$6:E$37))+SUMIF($B$6:$B$37,"Vacancy",E$6:E$37)+SUMIF($B$6:$B$37,"Concessions",E$6:E$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",E$6:E$37)+SUMIF($B$6:$B$37,"Delinquency",E$6:E$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",E$6:E$37)+SUMIF($B$6:$B$37,"Other Income",E$6:E$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",E$6:E$37)</f>
         <v/>
       </c>
       <c r="F39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",F$6:F$37),SUMIF($B$6:$B$37,"Gross Potential Rent",F$6:F$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",F$6:F$37))+SUMIF($B$6:$B$37,"Vacancy",F$6:F$37)+SUMIF($B$6:$B$37,"Concessions",F$6:F$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",F$6:F$37)+SUMIF($B$6:$B$37,"Delinquency",F$6:F$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",F$6:F$37)+SUMIF($B$6:$B$37,"Other Income",F$6:F$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",F$6:F$37)</f>
         <v/>
       </c>
       <c r="G39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",G$6:G$37),SUMIF($B$6:$B$37,"Gross Potential Rent",G$6:G$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",G$6:G$37))+SUMIF($B$6:$B$37,"Vacancy",G$6:G$37)+SUMIF($B$6:$B$37,"Concessions",G$6:G$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",G$6:G$37)+SUMIF($B$6:$B$37,"Delinquency",G$6:G$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",G$6:G$37)+SUMIF($B$6:$B$37,"Other Income",G$6:G$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",G$6:G$37)</f>
         <v/>
       </c>
       <c r="H39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",H$6:H$37),SUMIF($B$6:$B$37,"Gross Potential Rent",H$6:H$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",H$6:H$37))+SUMIF($B$6:$B$37,"Vacancy",H$6:H$37)+SUMIF($B$6:$B$37,"Concessions",H$6:H$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",H$6:H$37)+SUMIF($B$6:$B$37,"Delinquency",H$6:H$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",H$6:H$37)+SUMIF($B$6:$B$37,"Other Income",H$6:H$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",H$6:H$37)</f>
         <v/>
       </c>
       <c r="I39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",I$6:I$37),SUMIF($B$6:$B$37,"Gross Potential Rent",I$6:I$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",I$6:I$37))+SUMIF($B$6:$B$37,"Vacancy",I$6:I$37)+SUMIF($B$6:$B$37,"Concessions",I$6:I$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",I$6:I$37)+SUMIF($B$6:$B$37,"Delinquency",I$6:I$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",I$6:I$37)+SUMIF($B$6:$B$37,"Other Income",I$6:I$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",I$6:I$37)</f>
         <v/>
       </c>
       <c r="J39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",J$6:J$37),SUMIF($B$6:$B$37,"Gross Potential Rent",J$6:J$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",J$6:J$37))+SUMIF($B$6:$B$37,"Vacancy",J$6:J$37)+SUMIF($B$6:$B$37,"Concessions",J$6:J$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",J$6:J$37)+SUMIF($B$6:$B$37,"Delinquency",J$6:J$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",J$6:J$37)+SUMIF($B$6:$B$37,"Other Income",J$6:J$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",J$6:J$37)</f>
         <v/>
       </c>
       <c r="K39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",K$6:K$37),SUMIF($B$6:$B$37,"Gross Potential Rent",K$6:K$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",K$6:K$37))+SUMIF($B$6:$B$37,"Vacancy",K$6:K$37)+SUMIF($B$6:$B$37,"Concessions",K$6:K$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",K$6:K$37)+SUMIF($B$6:$B$37,"Delinquency",K$6:K$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",K$6:K$37)+SUMIF($B$6:$B$37,"Other Income",K$6:K$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",K$6:K$37)</f>
         <v/>
       </c>
       <c r="L39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",L$6:L$37),SUMIF($B$6:$B$37,"Gross Potential Rent",L$6:L$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",L$6:L$37))+SUMIF($B$6:$B$37,"Vacancy",L$6:L$37)+SUMIF($B$6:$B$37,"Concessions",L$6:L$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",L$6:L$37)+SUMIF($B$6:$B$37,"Delinquency",L$6:L$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",L$6:L$37)+SUMIF($B$6:$B$37,"Other Income",L$6:L$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",L$6:L$37)</f>
         <v/>
       </c>
       <c r="M39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",M$6:M$37),SUMIF($B$6:$B$37,"Gross Potential Rent",M$6:M$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",M$6:M$37))+SUMIF($B$6:$B$37,"Vacancy",M$6:M$37)+SUMIF($B$6:$B$37,"Concessions",M$6:M$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",M$6:M$37)+SUMIF($B$6:$B$37,"Delinquency",M$6:M$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",M$6:M$37)+SUMIF($B$6:$B$37,"Other Income",M$6:M$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",M$6:M$37)</f>
         <v/>
       </c>
       <c r="N39" s="11">
-        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain/(Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
+        <f>IF(COUNTIF($B$6:$B$37,"Gross Scheduled Rent")&gt;0,SUMIF($B$6:$B$37,"Gross Scheduled Rent",N$6:N$37),SUMIF($B$6:$B$37,"Gross Potential Rent",N$6:N$37)+SUMIF($B$6:$B$37,"Gain / (Loss) to Lease",N$6:N$37))+SUMIF($B$6:$B$37,"Vacancy",N$6:N$37)+SUMIF($B$6:$B$37,"Concessions",N$6:N$37)+SUMIF($B$6:$B$37,"Non-Revenue Units",N$6:N$37)+SUMIF($B$6:$B$37,"Delinquency",N$6:N$37)+SUMIF($B$6:$B$37,"Utility Reimbursements",N$6:N$37)+SUMIF($B$6:$B$37,"Other Income",N$6:N$37)+SUMIF($B$6:$B$37,"Revenue Adjustments",N$6:N$37)</f>
         <v/>
       </c>
       <c r="O39" s="11">
@@ -2616,7 +2616,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Gain/(Loss) to Lease</t>
+          <t>Gain / (Loss) to Lease</t>
         </is>
       </c>
       <c r="B7" s="13">
@@ -2846,7 +2846,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>G&amp;A</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="B17" s="13">
@@ -3475,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3807,11 +3807,11 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>0.9833333333333333</v>
+          <t>Occupied units (physical)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>177</v>
       </c>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="17" t="n"/>
@@ -3822,166 +3822,152 @@
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>PHYSICAL occupancy: 177 of 180 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
+          <t>The source states no per-status unit table, so physical occupancy cannot be tied to it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Occupied units</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>177</v>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0.9833333333333333</v>
       </c>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="17" t="n"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>PHYSICAL occupancy: 177 of 180 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Market rent (monthly total)</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>The parse did not capture a per-unit market rent, so this cannot be tied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Occupied units</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>The numerator above, stated separately so the ratio can be re-derived.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>1/3 tie-outs OK; 1 NOT CHECKED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>1/5 tie-outs OK; 3 NOT CHECKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 177/180 units, physical. Down, model and employee units count as vacant.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Rent readback — 10 units, sampled reproducibly</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Our in-place rent</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Source cell value</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Source locator</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>A1-123</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F26</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>A1-130</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1438</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>1438</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F33</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>A2-108</t>
+          <t>A1-123</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1564</v>
+        <v>1417</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1564</v>
+        <v>1417</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F45</t>
+          <t>Rent Roll (source)!F26</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -3993,23 +3979,23 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>B1-101</t>
+          <t>A1-130</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1831</v>
+        <v>1438</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1831</v>
+        <v>1438</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F66</t>
+          <t>Rent Roll (source)!F33</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -4021,23 +4007,23 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>B1-103</t>
+          <t>A2-108</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1809</v>
+        <v>1564</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1809</v>
+        <v>1564</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F68</t>
+          <t>Rent Roll (source)!F45</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -4049,7 +4035,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>B1-113</t>
+          <t>B1-101</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4058,14 +4044,14 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1734</v>
+        <v>1831</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1734</v>
+        <v>1831</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F78</t>
+          <t>Rent Roll (source)!F66</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -4077,7 +4063,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>B1-126</t>
+          <t>B1-103</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4086,14 +4072,14 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F91</t>
+          <t>Rent Roll (source)!F68</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -4105,23 +4091,23 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>B2-123</t>
+          <t>B1-113</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1887</v>
+        <v>1734</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1887</v>
+        <v>1734</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F130</t>
+          <t>Rent Roll (source)!F78</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -4133,23 +4119,23 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>C1-118</t>
+          <t>B1-126</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>2056</v>
+        <v>1799</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>2056</v>
+        <v>1799</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F161</t>
+          <t>Rent Roll (source)!F91</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -4161,288 +4147,344 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>B2-123</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F130</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>C1-118</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F161</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Cypress-106</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Cypress TH</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C39" s="6" t="n">
         <v>2343</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D39" s="6" t="n">
         <v>2343</v>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Rent Roll (source)!F175</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-06-30|180), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Pricing and cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Price per unit</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Unit count</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>180</v>
-      </c>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Total purchase price</t>
-        </is>
-      </c>
-      <c r="B45" s="6">
-        <f>B43*B44</f>
-        <v/>
+          <t>Price per unit</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
+          <t>Total purchase price</t>
         </is>
       </c>
       <c r="B47" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>T-12 operating expenses</t>
-        </is>
-      </c>
-      <c r="B48" s="6">
-        <f>'P&amp;L Summary'!B29</f>
+        <f>B45*B46</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>T-12 net operating income</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B49" s="6">
-        <f>'P&amp;L Summary'!B30</f>
+        <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>T-12 cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B50" s="21">
-        <f>IFERROR(B49/B45,"")</f>
+          <t>T-12 operating expenses</t>
+        </is>
+      </c>
+      <c r="B50" s="6">
+        <f>'P&amp;L Summary'!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>T-12 net operating income</t>
+        </is>
+      </c>
+      <c r="B51" s="6">
+        <f>'P&amp;L Summary'!B30</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized revenue</t>
-        </is>
-      </c>
-      <c r="B52" s="6">
-        <f>'P&amp;L Summary'!C16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>T-3 annualized operating expenses</t>
-        </is>
-      </c>
-      <c r="B53" s="6">
-        <f>'P&amp;L Summary'!C29</f>
+          <t>T-12 cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B52" s="21">
+        <f>IFERROR(B51/B47,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized net operating income</t>
+          <t>T-3 annualized revenue</t>
         </is>
       </c>
       <c r="B54" s="6">
-        <f>'P&amp;L Summary'!C30</f>
+        <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B55" s="21">
-        <f>IFERROR(B54/B45,"")</f>
+          <t>T-3 annualized operating expenses</t>
+        </is>
+      </c>
+      <c r="B55" s="6">
+        <f>'P&amp;L Summary'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized net operating income</t>
+        </is>
+      </c>
+      <c r="B56" s="6">
+        <f>'P&amp;L Summary'!C30</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma revenue</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>4051427.88</v>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>Kept in its own block; never merged into the T-12.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Broker pro forma operating expenses</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>1718834.16</v>
+          <t>T-3 annualized cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B57" s="21">
+        <f>IFERROR(B56/B47,"")</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma net operating income</t>
+          <t>Broker pro forma revenue</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>2332593.72</v>
+        <v>4051427.88</v>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>Kept in its own block; never merged into the T-12.</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
+          <t>Broker pro forma operating expenses</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>1718834.16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Broker pro forma net operating income</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>2332593.72</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
           <t>Broker pro forma cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B60" s="21">
-        <f>IFERROR(B59/B45,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="B62" s="21">
+        <f>IFERROR(B61/B47,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>Revenue trend</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B63" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>T-6 revenue (annualized)</t>
-        </is>
-      </c>
-      <c r="B64" s="6">
-        <f>SUM('T-12 Data'!I39:N39)*2</f>
-        <v/>
-      </c>
-      <c r="C64" s="20" t="inlineStr">
-        <is>
-          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
-        </is>
-      </c>
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>T-3 revenue (annualized)</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B65" s="6">
-        <f>'P&amp;L Summary'!C16</f>
+        <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>T-6 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B66" s="6">
+        <f>SUM('T-12 Data'!I39:N39)*2</f>
+        <v/>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>T-3 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B67" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B66" s="19">
-        <f>IFERROR(B65/B47-1,"")</f>
-        <v/>
-      </c>
-      <c r="C66" s="20" t="inlineStr">
+      <c r="B68" s="19">
+        <f>IFERROR(B67/B49-1,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -3475,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3871,115 +3871,107 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Occupied units</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>177</v>
-      </c>
+          <t>Duplicate rows: kept the in-place lease</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>The export lists no unit twice, so there is no row choice to make.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Occupied units</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>The numerator above, stated separately so the ratio can be re-derived.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>1/5 tie-outs OK; 3 NOT CHECKED</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>1/6 tie-outs OK; 4 NOT CHECKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 177/180 units, physical. Down, model and employee units count as vacant.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Rent readback — 10 units, sampled reproducibly</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Our in-place rent</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Source cell value</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Source locator</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>A1-123</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F26</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>A1-130</t>
+          <t>A1-123</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3988,14 +3980,14 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1438</v>
+        <v>1417</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1438</v>
+        <v>1417</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F33</t>
+          <t>Rent Roll (source)!F26</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -4007,23 +3999,23 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>A2-108</t>
+          <t>A1-130</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1564</v>
+        <v>1438</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1564</v>
+        <v>1438</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F45</t>
+          <t>Rent Roll (source)!F33</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -4035,23 +4027,23 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>B1-101</t>
+          <t>A2-108</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1831</v>
+        <v>1564</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1831</v>
+        <v>1564</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F66</t>
+          <t>Rent Roll (source)!F45</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -4063,7 +4055,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>B1-103</t>
+          <t>B1-101</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4072,14 +4064,14 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1809</v>
+        <v>1831</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1809</v>
+        <v>1831</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F68</t>
+          <t>Rent Roll (source)!F66</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -4091,7 +4083,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>B1-113</t>
+          <t>B1-103</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -4100,14 +4092,14 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1734</v>
+        <v>1809</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1734</v>
+        <v>1809</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F78</t>
+          <t>Rent Roll (source)!F68</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -4119,7 +4111,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>B1-126</t>
+          <t>B1-113</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -4128,14 +4120,14 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1799</v>
+        <v>1734</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1799</v>
+        <v>1734</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F91</t>
+          <t>Rent Roll (source)!F78</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -4147,23 +4139,23 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>B2-123</t>
+          <t>B1-126</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1887</v>
+        <v>1799</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1887</v>
+        <v>1799</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F130</t>
+          <t>Rent Roll (source)!F91</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -4175,23 +4167,23 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>C1-118</t>
+          <t>B2-123</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>2056</v>
+        <v>1887</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>2056</v>
+        <v>1887</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F161</t>
+          <t>Rent Roll (source)!F130</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -4203,288 +4195,316 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>C1-118</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F161</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Cypress-106</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Cypress TH</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C40" s="6" t="n">
         <v>2343</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D40" s="6" t="n">
         <v>2343</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Rent Roll (source)!F175</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-06-30|180), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Pricing and cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Price per unit</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
-        </is>
-      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Unit count</t>
+          <t>Price per unit</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>180</v>
+        <v>215000</v>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
           <t>Total purchase price</t>
         </is>
       </c>
-      <c r="B47" s="6">
-        <f>B45*B46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B49" s="6">
-        <f>'P&amp;L Summary'!B16</f>
+      <c r="B48" s="6">
+        <f>B46*B47</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>T-12 operating expenses</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B50" s="6">
-        <f>'P&amp;L Summary'!B29</f>
+        <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>T-12 net operating income</t>
+          <t>T-12 operating expenses</t>
         </is>
       </c>
       <c r="B51" s="6">
-        <f>'P&amp;L Summary'!B30</f>
+        <f>'P&amp;L Summary'!B29</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>T-12 net operating income</t>
+        </is>
+      </c>
+      <c r="B52" s="6">
+        <f>'P&amp;L Summary'!B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>T-12 cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B52" s="21">
-        <f>IFERROR(B51/B47,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>T-3 annualized revenue</t>
-        </is>
-      </c>
-      <c r="B54" s="6">
-        <f>'P&amp;L Summary'!C16</f>
+      <c r="B53" s="21">
+        <f>IFERROR(B52/B48,"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized operating expenses</t>
+          <t>T-3 annualized revenue</t>
         </is>
       </c>
       <c r="B55" s="6">
-        <f>'P&amp;L Summary'!C29</f>
+        <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized net operating income</t>
+          <t>T-3 annualized operating expenses</t>
         </is>
       </c>
       <c r="B56" s="6">
-        <f>'P&amp;L Summary'!C30</f>
+        <f>'P&amp;L Summary'!C29</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
+          <t>T-3 annualized net operating income</t>
+        </is>
+      </c>
+      <c r="B57" s="6">
+        <f>'P&amp;L Summary'!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
           <t>T-3 annualized cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B57" s="21">
-        <f>IFERROR(B56/B47,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Broker pro forma revenue</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>4051427.88</v>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>Kept in its own block; never merged into the T-12.</t>
-        </is>
+      <c r="B58" s="21">
+        <f>IFERROR(B57/B48,"")</f>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma operating expenses</t>
+          <t>Broker pro forma revenue</t>
         </is>
       </c>
       <c r="B60" s="6" t="n">
-        <v>1718834.16</v>
+        <v>4051427.88</v>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Kept in its own block; never merged into the T-12.</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma net operating income</t>
+          <t>Broker pro forma operating expenses</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>2332593.72</v>
+        <v>1718834.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
+          <t>Broker pro forma net operating income</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>2332593.72</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
           <t>Broker pro forma cap rate (illustrative)</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IFERROR(B61/B47,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="B63" s="21">
+        <f>IFERROR(B62/B48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Revenue trend</t>
         </is>
       </c>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="16" t="n"/>
-      <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B65" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
-      </c>
+      <c r="B65" s="16" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="16" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>T-6 revenue (annualized)</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B66" s="6">
-        <f>SUM('T-12 Data'!I39:N39)*2</f>
-        <v/>
-      </c>
-      <c r="C66" s="20" t="inlineStr">
-        <is>
-          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
-        </is>
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>T-3 revenue (annualized)</t>
+          <t>T-6 revenue (annualized)</t>
         </is>
       </c>
       <c r="B67" s="6">
-        <f>'P&amp;L Summary'!C16</f>
-        <v/>
+        <f>SUM('T-12 Data'!I39:N39)*2</f>
+        <v/>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>T-3 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B68" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B68" s="19">
-        <f>IFERROR(B67/B49-1,"")</f>
-        <v/>
-      </c>
-      <c r="C68" s="20" t="inlineStr">
+      <c r="B69" s="19">
+        <f>IFERROR(B68/B50-1,"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -3854,17 +3854,23 @@
           <t>Market rent (monthly total)</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>342300.5</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>342300.5</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>The parse did not capture a per-unit market rent, so this cannot be tied.</t>
+          <t>Validates row COMPLETENESS — 180 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 3 turnover pair(s) here carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
         </is>
       </c>
     </row>
@@ -3874,17 +3880,23 @@
           <t>Duplicate rows: kept the in-place lease</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
+      <c r="B23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>NOT CHECKED</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>The export lists no unit twice, so there is no row choice to make.</t>
+          <t>3 unit(s) listed twice; every one where an in-place row was available retained it (1 had none — D-NOCUR, where the alternative row carries no status and no rent, so keeping the other is correct). Keeping the other row instead would move in-place rent by $1,599/mo ($19,188/yr) — which the market-rent tie-out above cannot see.</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3925,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>1/6 tie-outs OK; 4 NOT CHECKED</t>
+          <t>3/6 tie-outs OK; 2 NOT CHECKED</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>Validates row COMPLETENESS — 180 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 3 turnover pair(s) here carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
+          <t>Validates row COMPLETENESS — 180 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 3 readable turnover pair(s) carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
         </is>
       </c>
     </row>
